--- a/data/course_data.xlsx
+++ b/data/course_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63289AB0-56F6-47B5-BD19-022E00C6CFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FFED06-5DA2-476A-AFE7-B2228BAC54D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1820" yWindow="1820" windowWidth="24460" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/course_data.xlsx
+++ b/data/course_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FFED06-5DA2-476A-AFE7-B2228BAC54D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DF911E-D6D4-47B0-9A8B-A7BB15E2721D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17190" yWindow="6060" windowWidth="16320" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1470,7 +1470,7 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}" name="Table1" displayName="Table1" ref="A1:H227" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
   <autoFilter ref="A1:H227" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:H220">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H227">
     <sortCondition ref="B1:B227"/>
   </sortState>
   <tableColumns count="8">
@@ -1811,25 +1811,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>3435711</v>
+        <v>3979315</v>
       </c>
       <c r="G2" s="2">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -1837,25 +1837,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>373</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>374</v>
       </c>
       <c r="D3" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>2107934</v>
+        <v>1098471</v>
       </c>
       <c r="G3" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -1863,51 +1863,51 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>3048102</v>
+        <v>1307360</v>
       </c>
       <c r="G4" s="2">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2">
-        <v>1098471</v>
+        <v>2719999</v>
       </c>
       <c r="G5" s="2">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -1915,25 +1915,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>324</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>323</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2">
-        <v>2061533</v>
+        <v>1830239</v>
       </c>
       <c r="G6" s="2">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1941,25 +1941,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>385</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>386</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>2117533</v>
+        <v>1587825</v>
       </c>
       <c r="G7" s="2">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1967,51 +1967,51 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>350</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>351</v>
       </c>
       <c r="D8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8" s="2">
-        <v>3952988</v>
+        <v>2832797</v>
       </c>
       <c r="G8" s="2">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>351</v>
       </c>
       <c r="D9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="2">
-        <v>2719999</v>
+        <v>2832797</v>
       </c>
       <c r="G9" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -2019,25 +2019,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>309</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>308</v>
       </c>
       <c r="D10" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="2">
-        <v>2814410</v>
+        <v>3070901</v>
       </c>
       <c r="G10" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -2048,22 +2048,22 @@
         <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>198</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>199</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2">
-        <v>1463503</v>
+        <v>1666337</v>
       </c>
       <c r="G11" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -2074,22 +2074,22 @@
         <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>395</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>396</v>
       </c>
       <c r="D12" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2">
-        <v>2719999</v>
+        <v>4205238</v>
       </c>
       <c r="G12" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -2100,48 +2100,48 @@
         <v>27</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="2">
-        <v>1463803</v>
+        <v>1583231</v>
       </c>
       <c r="G13" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>204</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2">
-        <v>1029126</v>
+        <v>3070901</v>
       </c>
       <c r="G14" s="2">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -2149,25 +2149,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2">
-        <v>3218866</v>
+        <v>2355205</v>
       </c>
       <c r="G15" s="2">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -2175,13 +2175,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
@@ -2190,10 +2190,10 @@
         <v>13</v>
       </c>
       <c r="F16" s="2">
-        <v>3218866</v>
+        <v>3074554</v>
       </c>
       <c r="G16" s="2">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2">
         <v>0</v>
@@ -2201,25 +2201,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F17" s="2">
-        <v>2669297</v>
+        <v>1463803</v>
       </c>
       <c r="G17" s="2">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -2230,48 +2230,48 @@
         <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F18" s="2">
-        <v>1583231</v>
+        <v>3979315</v>
       </c>
       <c r="G18" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>372</v>
+        <v>68</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>371</v>
+        <v>69</v>
       </c>
       <c r="D19" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F19" s="2">
-        <v>2554019</v>
+        <v>3074554</v>
       </c>
       <c r="G19" s="2">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -2279,25 +2279,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="D20" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F20" s="2">
-        <v>1635809</v>
+        <v>4419464</v>
       </c>
       <c r="G20" s="2">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="H20" s="2">
         <v>0</v>
@@ -2305,25 +2305,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>412</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>413</v>
       </c>
       <c r="D21" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F21" s="2">
-        <v>1307360</v>
+        <v>2002083</v>
       </c>
       <c r="G21" s="2">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="H21" s="2">
         <v>0</v>
@@ -2331,25 +2331,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="2">
-        <v>2132049</v>
+        <v>2719999</v>
       </c>
       <c r="G22" s="2">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
@@ -2357,77 +2357,77 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="2">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1463503</v>
+      </c>
+      <c r="G23" s="2">
         <v>14</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="2">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="2">
-        <v>2669297</v>
-      </c>
-      <c r="G23" s="2">
-        <v>69</v>
-      </c>
       <c r="H23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F24" s="2">
-        <v>1684669</v>
+        <v>2002083</v>
       </c>
       <c r="G24" s="2">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="H24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>265</v>
+        <v>105</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>264</v>
+        <v>106</v>
       </c>
       <c r="D25" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F25" s="2">
-        <v>1041914</v>
+        <v>2433502</v>
       </c>
       <c r="G25" s="2">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
@@ -2435,25 +2435,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>61</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="D26" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F26" s="2">
-        <v>1498302</v>
+        <v>2355205</v>
       </c>
       <c r="G26" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -2461,13 +2461,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -2476,24 +2476,24 @@
         <v>10</v>
       </c>
       <c r="F27" s="2">
-        <v>1457877</v>
+        <v>9931948</v>
       </c>
       <c r="G27" s="2">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="H27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
@@ -2502,24 +2502,24 @@
         <v>10</v>
       </c>
       <c r="F28" s="2">
-        <v>1121323</v>
+        <v>9931948</v>
       </c>
       <c r="G28" s="2">
-        <v>203</v>
+        <v>147</v>
       </c>
       <c r="H28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
@@ -2528,10 +2528,10 @@
         <v>10</v>
       </c>
       <c r="F29" s="2">
-        <v>1410757</v>
+        <v>3143825</v>
       </c>
       <c r="G29" s="2">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -2539,25 +2539,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="D30" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2">
-        <v>3074554</v>
+        <v>9931948</v>
       </c>
       <c r="G30" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2565,13 +2565,13 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="D31" s="2">
         <v>2</v>
@@ -2580,36 +2580,36 @@
         <v>10</v>
       </c>
       <c r="F31" s="2">
-        <v>4392170</v>
+        <v>9931948</v>
       </c>
       <c r="G31" s="2">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F32" s="2">
-        <v>3074554</v>
+        <v>2238227</v>
       </c>
       <c r="G32" s="2">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -2617,25 +2617,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F33" s="2">
-        <v>1540100</v>
+        <v>3435711</v>
       </c>
       <c r="G33" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
@@ -2643,25 +2643,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="D34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F34" s="2">
-        <v>5715408</v>
+        <v>2903204</v>
       </c>
       <c r="G34" s="2">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
@@ -2669,25 +2669,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>78</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="D35" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F35" s="2">
-        <v>3261519</v>
+        <v>3013005</v>
       </c>
       <c r="G35" s="2">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="H35" s="2">
         <v>0</v>
@@ -2695,25 +2695,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F36" s="2">
-        <v>1498302</v>
+        <v>3013005</v>
       </c>
       <c r="G36" s="2">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -2724,22 +2724,22 @@
         <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="D37" s="2">
         <v>3</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F37" s="2">
-        <v>3013005</v>
+        <v>2238227</v>
       </c>
       <c r="G37" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -2750,51 +2750,51 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>85</v>
+        <v>363</v>
       </c>
       <c r="D38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F38" s="2">
-        <v>2238227</v>
+        <v>1267061</v>
       </c>
       <c r="G38" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="D39" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F39" s="2">
-        <v>1307360</v>
+        <v>2107934</v>
       </c>
       <c r="G39" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -2802,25 +2802,25 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>88</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="D40" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F40" s="2">
-        <v>9931948</v>
+        <v>3013005</v>
       </c>
       <c r="G40" s="2">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="H40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -2828,22 +2828,22 @@
         <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="D41" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F41" s="2">
-        <v>9931948</v>
+        <v>3143825</v>
       </c>
       <c r="G41" s="2">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
@@ -2854,22 +2854,22 @@
         <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>92</v>
+        <v>228</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>93</v>
+        <v>229</v>
       </c>
       <c r="D42" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F42" s="2">
-        <v>7248701</v>
+        <v>1842843</v>
       </c>
       <c r="G42" s="2">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2877,77 +2877,77 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>94</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>93</v>
+        <v>359</v>
       </c>
       <c r="D43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="2">
-        <v>4321939</v>
+        <v>3143825</v>
       </c>
       <c r="G43" s="2">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="H43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>95</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>96</v>
+        <v>355</v>
       </c>
       <c r="D44" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F44" s="2">
-        <v>1318658</v>
+        <v>7248701</v>
       </c>
       <c r="G44" s="2">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="H44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>98</v>
+        <v>213</v>
       </c>
       <c r="D45" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F45" s="2">
-        <v>3979315</v>
+        <v>2903204</v>
       </c>
       <c r="G45" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2955,25 +2955,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>99</v>
+        <v>336</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>100</v>
+        <v>337</v>
       </c>
       <c r="D46" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F46" s="2">
-        <v>3979315</v>
+        <v>2903204</v>
       </c>
       <c r="G46" s="2">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -2984,22 +2984,22 @@
         <v>7</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>101</v>
+        <v>283</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>102</v>
+        <v>284</v>
       </c>
       <c r="D47" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F47" s="2">
-        <v>9931948</v>
+        <v>1267061</v>
       </c>
       <c r="G47" s="2">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="H47" s="2">
         <v>1</v>
@@ -3007,25 +3007,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="D48" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F48" s="2">
-        <v>1235319</v>
+        <v>2238227</v>
       </c>
       <c r="G48" s="2">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -3033,13 +3033,13 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>105</v>
+        <v>214</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>106</v>
+        <v>215</v>
       </c>
       <c r="D49" s="2">
         <v>4</v>
@@ -3048,10 +3048,10 @@
         <v>13</v>
       </c>
       <c r="F49" s="2">
-        <v>2433502</v>
+        <v>2107934</v>
       </c>
       <c r="G49" s="2">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -3062,48 +3062,48 @@
         <v>7</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D50" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50" s="2">
-        <v>3143825</v>
+        <v>7248701</v>
       </c>
       <c r="G50" s="2">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="H50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>109</v>
+        <v>206</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="D51" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F51" s="2">
-        <v>2148154</v>
+        <v>2903204</v>
       </c>
       <c r="G51" s="2">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -3111,25 +3111,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>111</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>112</v>
+        <v>361</v>
       </c>
       <c r="D52" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F52" s="2">
-        <v>2148154</v>
+        <v>3435711</v>
       </c>
       <c r="G52" s="2">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -3137,25 +3137,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>299</v>
+        <v>94</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>300</v>
+        <v>93</v>
       </c>
       <c r="D53" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F53" s="2">
-        <v>1618088</v>
+        <v>4321939</v>
       </c>
       <c r="G53" s="2">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -3163,25 +3163,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D54" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F54" s="2">
-        <v>2903204</v>
+        <v>2148154</v>
       </c>
       <c r="G54" s="2">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -3189,25 +3189,25 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>398</v>
+        <v>128</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>399</v>
+        <v>129</v>
       </c>
       <c r="D55" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F55" s="2">
-        <v>2994200</v>
+        <v>1112262</v>
       </c>
       <c r="G55" s="2">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -3215,25 +3215,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>119</v>
+        <v>328</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>120</v>
+        <v>329</v>
       </c>
       <c r="D56" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F56" s="2">
-        <v>4270666</v>
+        <v>1112262</v>
       </c>
       <c r="G56" s="2">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -3241,25 +3241,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>121</v>
+        <v>334</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>120</v>
+        <v>335</v>
       </c>
       <c r="D57" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F57" s="2">
-        <v>5293627</v>
+        <v>1932179</v>
       </c>
       <c r="G57" s="2">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -3270,22 +3270,22 @@
         <v>21</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>122</v>
+        <v>356</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>123</v>
+        <v>357</v>
       </c>
       <c r="D58" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F58" s="2">
-        <v>7208507</v>
+        <v>2923606</v>
       </c>
       <c r="G58" s="2">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -3296,10 +3296,10 @@
         <v>21</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D59" s="2">
         <v>4</v>
@@ -3308,10 +3308,10 @@
         <v>13</v>
       </c>
       <c r="F59" s="2">
-        <v>2148154</v>
+        <v>1758752</v>
       </c>
       <c r="G59" s="2">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -3322,22 +3322,22 @@
         <v>21</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D60" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F60" s="2">
-        <v>2923606</v>
+        <v>3261519</v>
       </c>
       <c r="G60" s="2">
-        <v>159</v>
+        <v>49</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
@@ -3348,10 +3348,10 @@
         <v>21</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>128</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>129</v>
+        <v>409</v>
       </c>
       <c r="D61" s="2">
         <v>4</v>
@@ -3360,10 +3360,10 @@
         <v>13</v>
       </c>
       <c r="F61" s="2">
-        <v>1112262</v>
+        <v>7208507</v>
       </c>
       <c r="G61" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -3374,22 +3374,22 @@
         <v>21</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="D62" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F62" s="2">
-        <v>1540100</v>
+        <v>2814410</v>
       </c>
       <c r="G62" s="2">
-        <v>138</v>
+        <v>14</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -3397,25 +3397,25 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="D63" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F63" s="2">
-        <v>1618088</v>
+        <v>3041802</v>
       </c>
       <c r="G63" s="2">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="H63" s="2">
         <v>0</v>
@@ -3426,10 +3426,10 @@
         <v>21</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>134</v>
+        <v>340</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="D64" s="2">
         <v>4</v>
@@ -3438,10 +3438,10 @@
         <v>13</v>
       </c>
       <c r="F64" s="2">
-        <v>1758752</v>
+        <v>4321939</v>
       </c>
       <c r="G64" s="2">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="H64" s="2">
         <v>0</v>
@@ -3449,13 +3449,13 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="D65" s="2">
         <v>4</v>
@@ -3464,10 +3464,10 @@
         <v>13</v>
       </c>
       <c r="F65" s="2">
-        <v>2002083</v>
+        <v>3213466</v>
       </c>
       <c r="G65" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="D66" s="2">
         <v>4</v>
@@ -3490,10 +3490,10 @@
         <v>13</v>
       </c>
       <c r="F66" s="2">
-        <v>3524624</v>
+        <v>3369135</v>
       </c>
       <c r="G66" s="2">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H66" s="2">
         <v>0</v>
@@ -3501,13 +3501,13 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="D67" s="2">
         <v>4</v>
@@ -3516,10 +3516,10 @@
         <v>13</v>
       </c>
       <c r="F67" s="2">
-        <v>1090407</v>
+        <v>3261519</v>
       </c>
       <c r="G67" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
@@ -3527,25 +3527,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>303</v>
+        <v>50</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>304</v>
+        <v>51</v>
       </c>
       <c r="D68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F68" s="2">
-        <v>2832797</v>
+        <v>1635809</v>
       </c>
       <c r="G68" s="2">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="H68" s="2">
         <v>0</v>
@@ -3556,22 +3556,22 @@
         <v>21</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>144</v>
+        <v>261</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>145</v>
+        <v>262</v>
       </c>
       <c r="D69" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F69" s="2">
-        <v>3261519</v>
+        <v>4693090</v>
       </c>
       <c r="G69" s="2">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3582,22 +3582,22 @@
         <v>21</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="D70" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F70" s="2">
-        <v>3218866</v>
+        <v>1121323</v>
       </c>
       <c r="G70" s="2">
-        <v>124</v>
+        <v>203</v>
       </c>
       <c r="H70" s="2">
         <v>0</v>
@@ -3605,25 +3605,25 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="D71" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F71" s="2">
-        <v>9931948</v>
+        <v>2148154</v>
       </c>
       <c r="G71" s="2">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
@@ -3631,25 +3631,25 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F72" s="2">
-        <v>1600939</v>
+        <v>2923606</v>
       </c>
       <c r="G72" s="2">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -3657,13 +3657,13 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -3672,10 +3672,10 @@
         <v>10</v>
       </c>
       <c r="F73" s="2">
-        <v>2355205</v>
+        <v>1540100</v>
       </c>
       <c r="G73" s="2">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="H73" s="2">
         <v>0</v>
@@ -3683,25 +3683,25 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="D74" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F74" s="2">
-        <v>1767743</v>
+        <v>7208507</v>
       </c>
       <c r="G74" s="2">
-        <v>37</v>
+        <v>167</v>
       </c>
       <c r="H74" s="2">
         <v>0</v>
@@ -3709,25 +3709,25 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>272</v>
+        <v>109</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="D75" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F75" s="2">
-        <v>2579557</v>
+        <v>2148154</v>
       </c>
       <c r="G75" s="2">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H75" s="2">
         <v>0</v>
@@ -3735,25 +3735,25 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="D76" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F76" s="2">
-        <v>1385355</v>
+        <v>3261519</v>
       </c>
       <c r="G76" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="H76" s="2">
         <v>0</v>
@@ -3761,25 +3761,25 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>158</v>
+        <v>22</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="D77" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="2">
-        <v>1385355</v>
+        <v>2117533</v>
       </c>
       <c r="G77" s="2">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3787,25 +3787,25 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="D78" s="2">
         <v>3</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F78" s="2">
-        <v>3952988</v>
+        <v>1121323</v>
       </c>
       <c r="G78" s="2">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
@@ -3813,25 +3813,25 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>161</v>
+        <v>331</v>
       </c>
       <c r="D79" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F79" s="2">
-        <v>3496303</v>
+        <v>1029126</v>
       </c>
       <c r="G79" s="2">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3842,22 +3842,22 @@
         <v>21</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>163</v>
+        <v>332</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>164</v>
+        <v>333</v>
       </c>
       <c r="D80" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F80" s="2">
-        <v>3261519</v>
+        <v>1029126</v>
       </c>
       <c r="G80" s="2">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3865,13 +3865,13 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>165</v>
+        <v>352</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>166</v>
+        <v>353</v>
       </c>
       <c r="D81" s="2">
         <v>3</v>
@@ -3880,10 +3880,10 @@
         <v>13</v>
       </c>
       <c r="F81" s="2">
-        <v>4419464</v>
+        <v>4721220</v>
       </c>
       <c r="G81" s="2">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="H81" s="2">
         <v>0</v>
@@ -3891,25 +3891,25 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D82" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="2">
-        <v>1098471</v>
+        <v>3218866</v>
       </c>
       <c r="G82" s="2">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
@@ -3917,25 +3917,25 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="D83" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F83" s="2">
-        <v>2571190</v>
+        <v>1540100</v>
       </c>
       <c r="G83" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="H83" s="2">
         <v>0</v>
@@ -3943,25 +3943,25 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>171</v>
+        <v>314</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>172</v>
+        <v>315</v>
       </c>
       <c r="D84" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F84" s="2">
-        <v>1086552</v>
+        <v>4721220</v>
       </c>
       <c r="G84" s="2">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="H84" s="2">
         <v>0</v>
@@ -3969,25 +3969,25 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>173</v>
+        <v>38</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>174</v>
+        <v>39</v>
       </c>
       <c r="D85" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F85" s="2">
-        <v>1740446</v>
+        <v>1029126</v>
       </c>
       <c r="G85" s="2">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H85" s="2">
         <v>0</v>
@@ -3995,25 +3995,25 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="D86" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F86" s="2">
-        <v>2311022</v>
+        <v>3218866</v>
       </c>
       <c r="G86" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
@@ -4021,25 +4021,25 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>177</v>
+        <v>42</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="D87" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F87" s="2">
-        <v>1093367</v>
+        <v>3218866</v>
       </c>
       <c r="G87" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
@@ -4047,25 +4047,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="D88" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F88" s="2">
-        <v>5475421</v>
+        <v>3041802</v>
       </c>
       <c r="G88" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="H88" s="2">
         <v>0</v>
@@ -4073,25 +4073,25 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="D89" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F89" s="2">
-        <v>1767743</v>
+        <v>3261519</v>
       </c>
       <c r="G89" s="2">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H89" s="2">
         <v>0</v>
@@ -4102,22 +4102,22 @@
         <v>19</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="D90" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F90" s="2">
-        <v>1740446</v>
+        <v>3496303</v>
       </c>
       <c r="G90" s="2">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
@@ -4125,25 +4125,25 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>185</v>
+        <v>322</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>186</v>
+        <v>323</v>
       </c>
       <c r="D91" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>2137934</v>
+        <v>5320332</v>
       </c>
       <c r="G91" s="2">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -4151,25 +4151,25 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>187</v>
+        <v>322</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>188</v>
+        <v>323</v>
       </c>
       <c r="D92" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>1494406</v>
+        <v>5320332</v>
       </c>
       <c r="G92" s="2">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
@@ -4177,25 +4177,25 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>189</v>
+        <v>325</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="D93" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F93" s="2">
-        <v>3258742</v>
+        <v>5320332</v>
       </c>
       <c r="G93" s="2">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
@@ -4206,22 +4206,22 @@
         <v>21</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>191</v>
+        <v>325</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="D94" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F94" s="2">
-        <v>3369135</v>
+        <v>5320332</v>
       </c>
       <c r="G94" s="2">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
@@ -4229,25 +4229,25 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="D95" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F95" s="2">
-        <v>1457877</v>
+        <v>3850625</v>
       </c>
       <c r="G95" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4255,51 +4255,51 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>200</v>
+        <v>389</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>201</v>
+        <v>390</v>
       </c>
       <c r="D96" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F96" s="2">
-        <v>5299061</v>
+        <v>1047857</v>
       </c>
       <c r="G96" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>196</v>
+        <v>62</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="D97" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F97" s="2">
-        <v>2190106</v>
+        <v>1457877</v>
       </c>
       <c r="G97" s="2">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="H97" s="2">
         <v>0</v>
@@ -4307,25 +4307,25 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D98" s="2">
         <v>2</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F98" s="2">
-        <v>1666337</v>
+        <v>5475421</v>
       </c>
       <c r="G98" s="2">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="H98" s="2">
         <v>0</v>
@@ -4333,13 +4333,13 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>226</v>
+        <v>342</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>227</v>
+        <v>343</v>
       </c>
       <c r="D99" s="2">
         <v>3</v>
@@ -4348,10 +4348,10 @@
         <v>10</v>
       </c>
       <c r="F99" s="2">
-        <v>2576518</v>
+        <v>2137934</v>
       </c>
       <c r="G99" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H99" s="2">
         <v>0</v>
@@ -4359,25 +4359,25 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D100" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F100" s="2">
-        <v>3048102</v>
+        <v>1494406</v>
       </c>
       <c r="G100" s="2">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="H100" s="2">
         <v>0</v>
@@ -4385,13 +4385,13 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>204</v>
+        <v>397</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>205</v>
+        <v>396</v>
       </c>
       <c r="D101" s="2">
         <v>2</v>
@@ -4400,10 +4400,10 @@
         <v>10</v>
       </c>
       <c r="F101" s="2">
-        <v>3070901</v>
+        <v>5856415</v>
       </c>
       <c r="G101" s="2">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
@@ -4411,25 +4411,25 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>207</v>
+        <v>16</v>
       </c>
       <c r="D102" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F102" s="2">
-        <v>2903204</v>
+        <v>2061533</v>
       </c>
       <c r="G102" s="2">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="H102" s="2">
         <v>0</v>
@@ -4437,25 +4437,25 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>208</v>
+        <v>70</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
       <c r="D103" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F103" s="2">
-        <v>2238227</v>
+        <v>4392170</v>
       </c>
       <c r="G103" s="2">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H103" s="2">
         <v>0</v>
@@ -4463,51 +4463,51 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="D104" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F104" s="2">
-        <v>3143825</v>
+        <v>1740446</v>
       </c>
       <c r="G104" s="2">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="H104" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="D105" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F105" s="2">
-        <v>2903204</v>
+        <v>1767743</v>
       </c>
       <c r="G105" s="2">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="H105" s="2">
         <v>0</v>
@@ -4515,25 +4515,25 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="D106" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F106" s="2">
-        <v>2107934</v>
+        <v>3258742</v>
       </c>
       <c r="G106" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H106" s="2">
         <v>0</v>
@@ -4541,25 +4541,25 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>216</v>
+        <v>406</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>217</v>
+        <v>407</v>
       </c>
       <c r="D107" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F107" s="2">
-        <v>3013005</v>
+        <v>5930518</v>
       </c>
       <c r="G107" s="2">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H107" s="2">
         <v>0</v>
@@ -4567,25 +4567,25 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="D108" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F108" s="2">
-        <v>3261519</v>
+        <v>2571190</v>
       </c>
       <c r="G108" s="2">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H108" s="2">
         <v>0</v>
@@ -4593,25 +4593,25 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="D109" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F109" s="2">
-        <v>3041802</v>
+        <v>2311022</v>
       </c>
       <c r="G109" s="2">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="H109" s="2">
         <v>0</v>
@@ -4619,25 +4619,25 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="D110" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F110" s="2">
-        <v>3213466</v>
+        <v>2137934</v>
       </c>
       <c r="G110" s="2">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
@@ -4645,25 +4645,25 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="D111" s="2">
         <v>3</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F111" s="2">
-        <v>1707115</v>
+        <v>2571190</v>
       </c>
       <c r="G111" s="2">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
@@ -4671,25 +4671,25 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>228</v>
+        <v>381</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>229</v>
+        <v>382</v>
       </c>
       <c r="D112" s="2">
         <v>3</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F112" s="2">
-        <v>1842843</v>
+        <v>5475421</v>
       </c>
       <c r="G112" s="2">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
@@ -4697,13 +4697,13 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>387</v>
+        <v>154</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>388</v>
+        <v>155</v>
       </c>
       <c r="D113" s="2">
         <v>3</v>
@@ -4712,10 +4712,10 @@
         <v>13</v>
       </c>
       <c r="F113" s="2">
-        <v>1235319</v>
+        <v>1767743</v>
       </c>
       <c r="G113" s="2">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H113" s="2">
         <v>0</v>
@@ -4723,25 +4723,25 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>232</v>
+        <v>414</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>233</v>
+        <v>415</v>
       </c>
       <c r="D114" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F114" s="2">
-        <v>2977082</v>
+        <v>5856415</v>
       </c>
       <c r="G114" s="2">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="H114" s="2">
         <v>0</v>
@@ -4752,22 +4752,22 @@
         <v>19</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>234</v>
+        <v>316</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>235</v>
+        <v>317</v>
       </c>
       <c r="D115" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F115" s="2">
-        <v>3258742</v>
+        <v>1093367</v>
       </c>
       <c r="G115" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H115" s="2">
         <v>0</v>
@@ -4775,25 +4775,25 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>236</v>
+        <v>76</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="D116" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F116" s="2">
-        <v>6933704</v>
+        <v>5715408</v>
       </c>
       <c r="G116" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H116" s="2">
         <v>0</v>
@@ -4801,13 +4801,13 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>238</v>
+        <v>320</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="D117" s="2">
         <v>4</v>
@@ -4816,10 +4816,10 @@
         <v>13</v>
       </c>
       <c r="F117" s="2">
-        <v>2355205</v>
+        <v>1086552</v>
       </c>
       <c r="G117" s="2">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H117" s="2">
         <v>0</v>
@@ -4827,25 +4827,25 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>242</v>
+        <v>120</v>
       </c>
       <c r="D118" s="2">
         <v>3</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F118" s="2">
-        <v>4576344</v>
+        <v>5293627</v>
       </c>
       <c r="G118" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="H118" s="2">
         <v>0</v>
@@ -4853,13 +4853,13 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="D119" s="2">
         <v>4</v>
@@ -4868,10 +4868,10 @@
         <v>13</v>
       </c>
       <c r="F119" s="2">
-        <v>5318224</v>
+        <v>1093367</v>
       </c>
       <c r="G119" s="2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
@@ -4879,25 +4879,25 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>243</v>
+        <v>338</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>244</v>
+        <v>339</v>
       </c>
       <c r="D120" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F120" s="2">
-        <v>1410757</v>
+        <v>1086552</v>
       </c>
       <c r="G120" s="2">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="H120" s="2">
         <v>0</v>
@@ -4905,25 +4905,25 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>245</v>
+        <v>173</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="D121" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F121" s="2">
-        <v>2446060</v>
+        <v>1740446</v>
       </c>
       <c r="G121" s="2">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="H121" s="2">
         <v>0</v>
@@ -4931,25 +4931,25 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>247</v>
+        <v>364</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>248</v>
+        <v>365</v>
       </c>
       <c r="D122" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F122" s="2">
-        <v>1608770</v>
+        <v>2757489</v>
       </c>
       <c r="G122" s="2">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="H122" s="2">
         <v>0</v>
@@ -4960,22 +4960,22 @@
         <v>19</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>249</v>
+        <v>171</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="D123" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F123" s="2">
-        <v>2571190</v>
+        <v>1086552</v>
       </c>
       <c r="G123" s="2">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H123" s="2">
         <v>0</v>
@@ -4983,51 +4983,51 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="D124" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F124" s="2">
-        <v>1267061</v>
+        <v>2311022</v>
       </c>
       <c r="G124" s="2">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="H124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>251</v>
+        <v>169</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="D125" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F125" s="2">
-        <v>3074554</v>
+        <v>2571190</v>
       </c>
       <c r="G125" s="2">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="H125" s="2">
         <v>0</v>
@@ -5035,25 +5035,25 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>251</v>
+        <v>140</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>252</v>
+        <v>141</v>
       </c>
       <c r="D126" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F126" s="2">
-        <v>3074554</v>
+        <v>1090407</v>
       </c>
       <c r="G126" s="2">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H126" s="2">
         <v>0</v>
@@ -5061,13 +5061,13 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>251</v>
+        <v>370</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>252</v>
+        <v>371</v>
       </c>
       <c r="D127" s="2">
         <v>1</v>
@@ -5076,10 +5076,10 @@
         <v>10</v>
       </c>
       <c r="F127" s="2">
-        <v>2571190</v>
+        <v>1214802</v>
       </c>
       <c r="G127" s="2">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="H127" s="2">
         <v>0</v>
@@ -5087,51 +5087,51 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="D128" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F128" s="2">
-        <v>1494406</v>
+        <v>1684669</v>
       </c>
       <c r="G128" s="2">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="H128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="D129" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F129" s="2">
-        <v>1608770</v>
+        <v>2977082</v>
       </c>
       <c r="G129" s="2">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="H129" s="2">
         <v>0</v>
@@ -5142,22 +5142,22 @@
         <v>14</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>257</v>
+        <v>158</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="D130" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F130" s="2">
-        <v>2587917</v>
+        <v>1385355</v>
       </c>
       <c r="G130" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="H130" s="2">
         <v>0</v>
@@ -5165,25 +5165,25 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>259</v>
+        <v>158</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>260</v>
+        <v>159</v>
       </c>
       <c r="D131" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F131" s="2">
-        <v>4693090</v>
+        <v>1385355</v>
       </c>
       <c r="G131" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="H131" s="2">
         <v>0</v>
@@ -5191,13 +5191,13 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D132" s="2">
         <v>1</v>
@@ -5206,10 +5206,10 @@
         <v>10</v>
       </c>
       <c r="F132" s="2">
-        <v>4693090</v>
+        <v>1041914</v>
       </c>
       <c r="G132" s="2">
-        <v>203</v>
+        <v>110</v>
       </c>
       <c r="H132" s="2">
         <v>0</v>
@@ -5220,22 +5220,22 @@
         <v>14</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="D133" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F133" s="2">
-        <v>1041914</v>
+        <v>2391172</v>
       </c>
       <c r="G133" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="H133" s="2">
         <v>0</v>
@@ -5243,51 +5243,51 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>48</v>
+        <v>420</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>49</v>
+        <v>421</v>
       </c>
       <c r="D134" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F134" s="2">
-        <v>2579557</v>
+        <v>1021641</v>
       </c>
       <c r="G134" s="2">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="H134" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>266</v>
+        <v>15</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>267</v>
+        <v>16</v>
       </c>
       <c r="D135" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F135" s="2">
-        <v>3258742</v>
+        <v>3048102</v>
       </c>
       <c r="G135" s="2">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="H135" s="2">
         <v>0</v>
@@ -5295,13 +5295,13 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>268</v>
+        <v>422</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>269</v>
+        <v>423</v>
       </c>
       <c r="D136" s="2">
         <v>2</v>
@@ -5310,10 +5310,10 @@
         <v>10</v>
       </c>
       <c r="F136" s="2">
-        <v>3633158</v>
+        <v>2092090</v>
       </c>
       <c r="G136" s="2">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="H136" s="2">
         <v>0</v>
@@ -5321,54 +5321,54 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>54</v>
+        <v>400</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>55</v>
+        <v>401</v>
       </c>
       <c r="D137" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F137" s="2">
-        <v>6112322</v>
+        <v>2458943</v>
       </c>
       <c r="G137" s="2">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="H137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>254</v>
+        <v>308</v>
       </c>
       <c r="D138" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F138" s="2">
-        <v>1618088</v>
+        <v>3258742</v>
       </c>
       <c r="G138" s="2">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="H138" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.35">
@@ -5376,22 +5376,22 @@
         <v>14</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>274</v>
+        <v>119</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>275</v>
+        <v>120</v>
       </c>
       <c r="D139" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F139" s="2">
-        <v>2550816</v>
+        <v>4270666</v>
       </c>
       <c r="G139" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H139" s="2">
         <v>0</v>
@@ -5399,25 +5399,25 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>274</v>
+        <v>44</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>275</v>
+        <v>45</v>
       </c>
       <c r="D140" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F140" s="2">
-        <v>2550816</v>
+        <v>2669297</v>
       </c>
       <c r="G140" s="2">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="H140" s="2">
         <v>0</v>
@@ -5425,25 +5425,25 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>383</v>
+        <v>95</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>384</v>
+        <v>96</v>
       </c>
       <c r="D141" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F141" s="2">
-        <v>1235319</v>
+        <v>1318658</v>
       </c>
       <c r="G141" s="2">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="H141" s="2">
         <v>0</v>
@@ -5451,25 +5451,25 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>274</v>
+        <v>391</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>276</v>
+        <v>392</v>
       </c>
       <c r="D142" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F142" s="2">
-        <v>4117613</v>
+        <v>1583231</v>
       </c>
       <c r="G142" s="2">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="H142" s="2">
         <v>0</v>
@@ -5477,25 +5477,25 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>277</v>
+        <v>377</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>278</v>
+        <v>378</v>
       </c>
       <c r="D143" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F143" s="2">
-        <v>4828331</v>
+        <v>1198965</v>
       </c>
       <c r="G143" s="2">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="H143" s="2">
         <v>0</v>
@@ -5503,25 +5503,25 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>277</v>
+        <v>379</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>278</v>
+        <v>380</v>
       </c>
       <c r="D144" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F144" s="2">
-        <v>1875741</v>
+        <v>1561186</v>
       </c>
       <c r="G144" s="2">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="H144" s="2">
         <v>0</v>
@@ -5529,51 +5529,51 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>277</v>
+        <v>56</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>278</v>
+        <v>57</v>
       </c>
       <c r="D145" s="2">
+        <v>3</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145" s="2">
+        <v>2669297</v>
+      </c>
+      <c r="G145" s="2">
+        <v>69</v>
+      </c>
+      <c r="H145" s="2">
         <v>1</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F145" s="2">
-        <v>1875741</v>
-      </c>
-      <c r="G145" s="2">
-        <v>189</v>
-      </c>
-      <c r="H145" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>279</v>
+        <v>202</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>280</v>
+        <v>203</v>
       </c>
       <c r="D146" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F146" s="2">
-        <v>1457877</v>
+        <v>3048102</v>
       </c>
       <c r="G146" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H146" s="2">
         <v>0</v>
@@ -5581,25 +5581,25 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>281</v>
+        <v>430</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>282</v>
+        <v>431</v>
       </c>
       <c r="D147" s="2">
         <v>3</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F147" s="2">
-        <v>1009202</v>
+        <v>2977082</v>
       </c>
       <c r="G147" s="2">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="H147" s="2">
         <v>0</v>
@@ -5607,51 +5607,51 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>283</v>
+        <v>418</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>284</v>
+        <v>419</v>
       </c>
       <c r="D148" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F148" s="2">
-        <v>1267061</v>
+        <v>5213213</v>
       </c>
       <c r="G148" s="2">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D149" s="2">
         <v>4</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F149" s="2">
-        <v>3041802</v>
+        <v>6933704</v>
       </c>
       <c r="G149" s="2">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2">
         <v>0</v>
@@ -5659,25 +5659,25 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>287</v>
+        <v>138</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>288</v>
+        <v>139</v>
       </c>
       <c r="D150" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F150" s="2">
-        <v>1121323</v>
+        <v>3524624</v>
       </c>
       <c r="G150" s="2">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H150" s="2">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         <v>14</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="D151" s="2">
         <v>4</v>
@@ -5700,10 +5700,10 @@
         <v>13</v>
       </c>
       <c r="F151" s="2">
-        <v>2028216</v>
+        <v>2587917</v>
       </c>
       <c r="G151" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H151" s="2">
         <v>0</v>
@@ -5711,25 +5711,25 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>291</v>
+        <v>366</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>292</v>
+        <v>367</v>
       </c>
       <c r="D152" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F152" s="2">
-        <v>1009202</v>
+        <v>2092090</v>
       </c>
       <c r="G152" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H152" s="2">
         <v>0</v>
@@ -5737,25 +5737,25 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>293</v>
+        <v>402</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>294</v>
+        <v>403</v>
       </c>
       <c r="D153" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F153" s="2">
-        <v>3013005</v>
+        <v>2234229</v>
       </c>
       <c r="G153" s="2">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
@@ -5763,13 +5763,13 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>295</v>
+        <v>410</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>296</v>
+        <v>411</v>
       </c>
       <c r="D154" s="2">
         <v>4</v>
@@ -5778,10 +5778,10 @@
         <v>13</v>
       </c>
       <c r="F154" s="2">
-        <v>2311022</v>
+        <v>1214802</v>
       </c>
       <c r="G154" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H154" s="2">
         <v>0</v>
@@ -5792,22 +5792,22 @@
         <v>14</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>297</v>
+        <v>426</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>298</v>
+        <v>427</v>
       </c>
       <c r="D155" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F155" s="2">
-        <v>2391172</v>
+        <v>3524624</v>
       </c>
       <c r="G155" s="2">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -5815,13 +5815,13 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>150</v>
+        <v>289</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>151</v>
+        <v>290</v>
       </c>
       <c r="D156" s="2">
         <v>4</v>
@@ -5830,10 +5830,10 @@
         <v>13</v>
       </c>
       <c r="F156" s="2">
-        <v>5018255</v>
+        <v>2028216</v>
       </c>
       <c r="G156" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H156" s="2">
         <v>0</v>
@@ -5841,13 +5841,13 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>156</v>
+        <v>305</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>157</v>
+        <v>306</v>
       </c>
       <c r="D157" s="2">
         <v>4</v>
@@ -5856,10 +5856,10 @@
         <v>13</v>
       </c>
       <c r="F157" s="2">
-        <v>5018255</v>
+        <v>3979315</v>
       </c>
       <c r="G157" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
@@ -5867,13 +5867,13 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="D158" s="2">
         <v>4</v>
@@ -5882,10 +5882,10 @@
         <v>13</v>
       </c>
       <c r="F158" s="2">
-        <v>2994200</v>
+        <v>3258742</v>
       </c>
       <c r="G158" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H158" s="2">
         <v>0</v>
@@ -5893,25 +5893,25 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>306</v>
+        <v>168</v>
       </c>
       <c r="D159" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F159" s="2">
-        <v>3979315</v>
+        <v>1098471</v>
       </c>
       <c r="G159" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H159" s="2">
         <v>0</v>
@@ -5919,54 +5919,54 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>307</v>
+        <v>61</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>308</v>
+        <v>59</v>
       </c>
       <c r="D160" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F160" s="2">
-        <v>3258742</v>
+        <v>1498302</v>
       </c>
       <c r="G160" s="2">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="H160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>309</v>
+        <v>66</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>308</v>
+        <v>67</v>
       </c>
       <c r="D161" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F161" s="2">
-        <v>3070901</v>
+        <v>1410757</v>
       </c>
       <c r="G161" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.35">
@@ -5974,22 +5974,22 @@
         <v>17</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>310</v>
+        <v>18</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>311</v>
+        <v>16</v>
       </c>
       <c r="D162" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F162" s="2">
-        <v>3633158</v>
+        <v>1098471</v>
       </c>
       <c r="G162" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H162" s="2">
         <v>0</v>
@@ -5997,25 +5997,25 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>313</v>
+        <v>244</v>
       </c>
       <c r="D163" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F163" s="2">
-        <v>3850625</v>
+        <v>1410757</v>
       </c>
       <c r="G163" s="2">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="H163" s="2">
         <v>0</v>
@@ -6023,25 +6023,25 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>315</v>
+        <v>269</v>
       </c>
       <c r="D164" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F164" s="2">
-        <v>4721220</v>
+        <v>3633158</v>
       </c>
       <c r="G164" s="2">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="H164" s="2">
         <v>0</v>
@@ -6049,25 +6049,25 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="D165" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F165" s="2">
-        <v>1093367</v>
+        <v>1009202</v>
       </c>
       <c r="G165" s="2">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H165" s="2">
         <v>0</v>
@@ -6075,25 +6075,25 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>319</v>
+        <v>376</v>
       </c>
       <c r="D166" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F166" s="2">
-        <v>2238227</v>
+        <v>1410757</v>
       </c>
       <c r="G166" s="2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H166" s="2">
         <v>0</v>
@@ -6101,25 +6101,25 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>320</v>
+        <v>196</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>321</v>
+        <v>197</v>
       </c>
       <c r="D167" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F167" s="2">
-        <v>1086552</v>
+        <v>2190106</v>
       </c>
       <c r="G167" s="2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="H167" s="2">
         <v>0</v>
@@ -6127,25 +6127,25 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
       <c r="D168" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F168" s="2">
-        <v>5320332</v>
+        <v>1009202</v>
       </c>
       <c r="G168" s="2">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -6153,25 +6153,25 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="D169" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F169" s="2">
-        <v>1830239</v>
+        <v>2446060</v>
       </c>
       <c r="G169" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H169" s="2">
         <v>0</v>
@@ -6179,25 +6179,25 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>322</v>
+        <v>428</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>323</v>
+        <v>429</v>
       </c>
       <c r="D170" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F170" s="2">
-        <v>5320332</v>
+        <v>1892200</v>
       </c>
       <c r="G170" s="2">
-        <v>181</v>
+        <v>5</v>
       </c>
       <c r="H170" s="2">
         <v>0</v>
@@ -6205,25 +6205,25 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>325</v>
+        <v>245</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>326</v>
+        <v>246</v>
       </c>
       <c r="D171" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F171" s="2">
-        <v>5320332</v>
+        <v>2446060</v>
       </c>
       <c r="G171" s="2">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="H171" s="2">
         <v>0</v>
@@ -6231,25 +6231,25 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>325</v>
+        <v>247</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>327</v>
+        <v>248</v>
       </c>
       <c r="D172" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F172" s="2">
-        <v>5320332</v>
+        <v>1608770</v>
       </c>
       <c r="G172" s="2">
-        <v>146</v>
+        <v>5</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -6257,25 +6257,25 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="D173" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F173" s="2">
-        <v>1112262</v>
+        <v>3633158</v>
       </c>
       <c r="G173" s="2">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="H173" s="2">
         <v>0</v>
@@ -6283,25 +6283,25 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>330</v>
+        <v>255</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>331</v>
+        <v>256</v>
       </c>
       <c r="D174" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F174" s="2">
-        <v>1029126</v>
+        <v>1608770</v>
       </c>
       <c r="G174" s="2">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="H174" s="2">
         <v>0</v>
@@ -6309,25 +6309,25 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>332</v>
+        <v>266</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>333</v>
+        <v>267</v>
       </c>
       <c r="D175" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F175" s="2">
-        <v>1029126</v>
+        <v>3258742</v>
       </c>
       <c r="G175" s="2">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="H175" s="2">
         <v>0</v>
@@ -6335,25 +6335,25 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>335</v>
+        <v>425</v>
       </c>
       <c r="D176" s="2">
         <v>4</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F176" s="2">
-        <v>1932179</v>
+        <v>5997408</v>
       </c>
       <c r="G176" s="2">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H176" s="2">
         <v>0</v>
@@ -6361,13 +6361,13 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="D177" s="2">
         <v>4</v>
@@ -6376,10 +6376,10 @@
         <v>13</v>
       </c>
       <c r="F177" s="2">
-        <v>2903204</v>
+        <v>1498302</v>
       </c>
       <c r="G177" s="2">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H177" s="2">
         <v>0</v>
@@ -6387,25 +6387,25 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>339</v>
+        <v>405</v>
       </c>
       <c r="D178" s="2">
         <v>4</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F178" s="2">
-        <v>1086552</v>
+        <v>1410757</v>
       </c>
       <c r="G178" s="2">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="H178" s="2">
         <v>0</v>
@@ -6413,51 +6413,51 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>340</v>
+        <v>251</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>341</v>
+        <v>252</v>
       </c>
       <c r="D179" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F179" s="2">
-        <v>4321939</v>
+        <v>1267061</v>
       </c>
       <c r="G179" s="2">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="H179" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>342</v>
+        <v>251</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>343</v>
+        <v>252</v>
       </c>
       <c r="D180" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F180" s="2">
-        <v>2137934</v>
+        <v>3074554</v>
       </c>
       <c r="G180" s="2">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H180" s="2">
         <v>0</v>
@@ -6465,25 +6465,25 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="D181" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F181" s="2">
-        <v>2576518</v>
+        <v>3074554</v>
       </c>
       <c r="G181" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H181" s="2">
         <v>0</v>
@@ -6491,25 +6491,25 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>346</v>
+        <v>251</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>347</v>
+        <v>252</v>
       </c>
       <c r="D182" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F182" s="2">
-        <v>2446060</v>
+        <v>2571190</v>
       </c>
       <c r="G182" s="2">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
@@ -6520,48 +6520,48 @@
         <v>24</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>224</v>
+        <v>52</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>225</v>
+        <v>53</v>
       </c>
       <c r="D183" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F183" s="2">
-        <v>5299061</v>
+        <v>3952988</v>
       </c>
       <c r="G183" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="H183" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="D184" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F184" s="2">
-        <v>2832797</v>
+        <v>2554019</v>
       </c>
       <c r="G184" s="2">
-        <v>14</v>
+        <v>141</v>
       </c>
       <c r="H184" s="2">
         <v>0</v>
@@ -6569,25 +6569,25 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>351</v>
+        <v>59</v>
       </c>
       <c r="D185" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F185" s="2">
-        <v>2832797</v>
+        <v>1307360</v>
       </c>
       <c r="G185" s="2">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="H185" s="2">
         <v>0</v>
@@ -6595,25 +6595,25 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>352</v>
+        <v>162</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>353</v>
+        <v>161</v>
       </c>
       <c r="D186" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F186" s="2">
-        <v>4721220</v>
+        <v>2132049</v>
       </c>
       <c r="G186" s="2">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
@@ -6621,51 +6621,51 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>354</v>
+        <v>265</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>355</v>
+        <v>264</v>
       </c>
       <c r="D187" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F187" s="2">
-        <v>7248701</v>
+        <v>1041914</v>
       </c>
       <c r="G187" s="2">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="H187" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>356</v>
+        <v>301</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>357</v>
+        <v>302</v>
       </c>
       <c r="D188" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F188" s="2">
-        <v>2923606</v>
+        <v>1235319</v>
       </c>
       <c r="G188" s="2">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H188" s="2">
         <v>0</v>
@@ -6673,28 +6673,28 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>358</v>
+        <v>299</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="D189" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F189" s="2">
-        <v>3143825</v>
+        <v>1618088</v>
       </c>
       <c r="G189" s="2">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="H189" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.35">
@@ -6702,48 +6702,48 @@
         <v>24</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>348</v>
+        <v>398</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>349</v>
+        <v>399</v>
       </c>
       <c r="D190" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F190" s="2">
-        <v>2832797</v>
+        <v>2994200</v>
       </c>
       <c r="G190" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="H190" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>360</v>
+        <v>113</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>361</v>
+        <v>114</v>
       </c>
       <c r="D191" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F191" s="2">
-        <v>3435711</v>
+        <v>1618088</v>
       </c>
       <c r="G191" s="2">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
@@ -6751,51 +6751,51 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>362</v>
+        <v>303</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="D192" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F192" s="2">
-        <v>1267061</v>
+        <v>2832797</v>
       </c>
       <c r="G192" s="2">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H192" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>364</v>
+        <v>132</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>365</v>
+        <v>133</v>
       </c>
       <c r="D193" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F193" s="2">
-        <v>2757489</v>
+        <v>1600939</v>
       </c>
       <c r="G193" s="2">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -6803,25 +6803,25 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>367</v>
+        <v>273</v>
       </c>
       <c r="D194" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F194" s="2">
-        <v>2092090</v>
+        <v>2579557</v>
       </c>
       <c r="G194" s="2">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
@@ -6832,22 +6832,22 @@
         <v>24</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>143</v>
+        <v>231</v>
       </c>
       <c r="D195" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F195" s="2">
-        <v>1502554</v>
+        <v>3952988</v>
       </c>
       <c r="G195" s="2">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="H195" s="2">
         <v>0</v>
@@ -6855,25 +6855,25 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>370</v>
+        <v>270</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>371</v>
+        <v>271</v>
       </c>
       <c r="D196" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F196" s="2">
-        <v>1214802</v>
+        <v>1457877</v>
       </c>
       <c r="G196" s="2">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="H196" s="2">
         <v>0</v>
@@ -6884,22 +6884,22 @@
         <v>24</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>416</v>
+        <v>200</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>417</v>
+        <v>201</v>
       </c>
       <c r="D197" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F197" s="2">
-        <v>3334973</v>
+        <v>5299061</v>
       </c>
       <c r="G197" s="2">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="H197" s="2">
         <v>0</v>
@@ -6907,25 +6907,25 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>373</v>
+        <v>226</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>374</v>
+        <v>227</v>
       </c>
       <c r="D198" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F198" s="2">
-        <v>1098471</v>
+        <v>2576518</v>
       </c>
       <c r="G198" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="H198" s="2">
         <v>0</v>
@@ -6933,25 +6933,25 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="D199" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F199" s="2">
-        <v>1410757</v>
+        <v>1707115</v>
       </c>
       <c r="G199" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H199" s="2">
         <v>0</v>
@@ -6959,25 +6959,25 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="D200" s="2">
         <v>3</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F200" s="2">
-        <v>1198965</v>
+        <v>1235319</v>
       </c>
       <c r="G200" s="2">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="H200" s="2">
         <v>0</v>
@@ -6985,25 +6985,25 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>379</v>
+        <v>241</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>380</v>
+        <v>242</v>
       </c>
       <c r="D201" s="2">
         <v>3</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F201" s="2">
-        <v>1561186</v>
+        <v>4576344</v>
       </c>
       <c r="G201" s="2">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="H201" s="2">
         <v>0</v>
@@ -7011,25 +7011,25 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>381</v>
+        <v>240</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>382</v>
+        <v>239</v>
       </c>
       <c r="D202" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F202" s="2">
-        <v>5475421</v>
+        <v>5318224</v>
       </c>
       <c r="G202" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
@@ -7040,10 +7040,10 @@
         <v>24</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>344</v>
+        <v>103</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>345</v>
+        <v>104</v>
       </c>
       <c r="D203" s="2">
         <v>4</v>
@@ -7052,10 +7052,10 @@
         <v>13</v>
       </c>
       <c r="F203" s="2">
-        <v>3371830</v>
+        <v>1494406</v>
       </c>
       <c r="G203" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H203" s="2">
         <v>0</v>
@@ -7063,28 +7063,28 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>385</v>
+        <v>48</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>386</v>
+        <v>49</v>
       </c>
       <c r="D204" s="2">
+        <v>4</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F204" s="2">
+        <v>2579557</v>
+      </c>
+      <c r="G204" s="2">
+        <v>16</v>
+      </c>
+      <c r="H204" s="2">
         <v>1</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F204" s="2">
-        <v>1587825</v>
-      </c>
-      <c r="G204" s="2">
-        <v>18</v>
-      </c>
-      <c r="H204" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.35">
@@ -7092,10 +7092,10 @@
         <v>24</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D205" s="2">
         <v>4</v>
@@ -7104,62 +7104,62 @@
         <v>13</v>
       </c>
       <c r="F205" s="2">
-        <v>1502554</v>
+        <v>6112322</v>
       </c>
       <c r="G205" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H205" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>389</v>
+        <v>253</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>390</v>
+        <v>254</v>
       </c>
       <c r="D206" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F206" s="2">
-        <v>1047857</v>
+        <v>1618088</v>
       </c>
       <c r="G206" s="2">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="H206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D207" s="2">
+        <v>4</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F207" s="2">
+        <v>1235319</v>
+      </c>
+      <c r="G207" s="2">
         <v>14</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D207" s="2">
-        <v>3</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F207" s="2">
-        <v>1583231</v>
-      </c>
-      <c r="G207" s="2">
-        <v>73</v>
       </c>
       <c r="H207" s="2">
         <v>0</v>
@@ -7167,25 +7167,25 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D208" s="2">
+        <v>4</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F208" s="2">
+        <v>1457877</v>
+      </c>
+      <c r="G208" s="2">
         <v>19</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D208" s="2">
-        <v>3</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F208" s="2">
-        <v>2571190</v>
-      </c>
-      <c r="G208" s="2">
-        <v>96</v>
       </c>
       <c r="H208" s="2">
         <v>0</v>
@@ -7193,25 +7193,25 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>395</v>
+        <v>150</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>396</v>
+        <v>151</v>
       </c>
       <c r="D209" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F209" s="2">
-        <v>4205238</v>
+        <v>5018255</v>
       </c>
       <c r="G209" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H209" s="2">
         <v>0</v>
@@ -7219,25 +7219,25 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D210" s="2">
+        <v>4</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F210" s="2">
+        <v>5018255</v>
+      </c>
+      <c r="G210" s="2">
         <v>19</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D210" s="2">
-        <v>2</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F210" s="2">
-        <v>5856415</v>
-      </c>
-      <c r="G210" s="2">
-        <v>91</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
@@ -7248,22 +7248,22 @@
         <v>24</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>274</v>
+        <v>117</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>276</v>
+        <v>118</v>
       </c>
       <c r="D211" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F211" s="2">
-        <v>1739868</v>
+        <v>2994200</v>
       </c>
       <c r="G211" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="H211" s="2">
         <v>0</v>
@@ -7271,25 +7271,25 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>400</v>
+        <v>192</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>401</v>
+        <v>193</v>
       </c>
       <c r="D212" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F212" s="2">
-        <v>2458943</v>
+        <v>2576518</v>
       </c>
       <c r="G212" s="2">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="H212" s="2">
         <v>0</v>
@@ -7297,13 +7297,13 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>402</v>
+        <v>224</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>403</v>
+        <v>225</v>
       </c>
       <c r="D213" s="2">
         <v>4</v>
@@ -7312,10 +7312,10 @@
         <v>13</v>
       </c>
       <c r="F213" s="2">
-        <v>2234229</v>
+        <v>5299061</v>
       </c>
       <c r="G213" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H213" s="2">
         <v>0</v>
@@ -7323,13 +7323,13 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>404</v>
+        <v>348</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>405</v>
+        <v>349</v>
       </c>
       <c r="D214" s="2">
         <v>4</v>
@@ -7338,36 +7338,36 @@
         <v>13</v>
       </c>
       <c r="F214" s="2">
-        <v>1410757</v>
+        <v>2832797</v>
       </c>
       <c r="G214" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H214" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>406</v>
+        <v>142</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>407</v>
+        <v>143</v>
       </c>
       <c r="D215" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F215" s="2">
-        <v>5930518</v>
+        <v>1502554</v>
       </c>
       <c r="G215" s="2">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H215" s="2">
         <v>0</v>
@@ -7375,13 +7375,13 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D216" s="2">
         <v>4</v>
@@ -7390,10 +7390,10 @@
         <v>13</v>
       </c>
       <c r="F216" s="2">
-        <v>7208507</v>
+        <v>3334973</v>
       </c>
       <c r="G216" s="2">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="H216" s="2">
         <v>0</v>
@@ -7401,13 +7401,13 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>411</v>
+        <v>345</v>
       </c>
       <c r="D217" s="2">
         <v>4</v>
@@ -7416,10 +7416,10 @@
         <v>13</v>
       </c>
       <c r="F217" s="2">
-        <v>1214802</v>
+        <v>3371830</v>
       </c>
       <c r="G217" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H217" s="2">
         <v>0</v>
@@ -7427,25 +7427,25 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>412</v>
+        <v>25</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>413</v>
+        <v>26</v>
       </c>
       <c r="D218" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F218" s="2">
-        <v>2002083</v>
+        <v>1502554</v>
       </c>
       <c r="G218" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H218" s="2">
         <v>0</v>
@@ -7453,25 +7453,25 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>414</v>
+        <v>277</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>415</v>
+        <v>278</v>
       </c>
       <c r="D219" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F219" s="2">
-        <v>5856415</v>
+        <v>4828331</v>
       </c>
       <c r="G219" s="2">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="H219" s="2">
         <v>0</v>
@@ -7479,25 +7479,25 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>195</v>
+        <v>278</v>
       </c>
       <c r="D220" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F220" s="2">
-        <v>1210302</v>
+        <v>1875741</v>
       </c>
       <c r="G220" s="2">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H220" s="2">
         <v>0</v>
@@ -7505,25 +7505,25 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>418</v>
+        <v>277</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>419</v>
+        <v>278</v>
       </c>
       <c r="D221" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F221" s="2">
-        <v>5213213</v>
+        <v>1875741</v>
       </c>
       <c r="G221" s="2">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
@@ -7534,22 +7534,22 @@
         <v>14</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>420</v>
+        <v>274</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>421</v>
+        <v>275</v>
       </c>
       <c r="D222" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F222" s="2">
-        <v>1021641</v>
+        <v>2550816</v>
       </c>
       <c r="G222" s="2">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="H222" s="2">
         <v>0</v>
@@ -7557,25 +7557,25 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>422</v>
+        <v>274</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>423</v>
+        <v>275</v>
       </c>
       <c r="D223" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F223" s="2">
-        <v>2092090</v>
+        <v>2550816</v>
       </c>
       <c r="G223" s="2">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="H223" s="2">
         <v>0</v>
@@ -7583,25 +7583,25 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>425</v>
+        <v>276</v>
       </c>
       <c r="D224" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F224" s="2">
-        <v>5997408</v>
+        <v>4117613</v>
       </c>
       <c r="G224" s="2">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="H224" s="2">
         <v>0</v>
@@ -7609,25 +7609,25 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>426</v>
+        <v>274</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="D225" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F225" s="2">
-        <v>3524624</v>
+        <v>1739868</v>
       </c>
       <c r="G225" s="2">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="H225" s="2">
         <v>0</v>
@@ -7635,25 +7635,25 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>428</v>
+        <v>259</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>429</v>
+        <v>260</v>
       </c>
       <c r="D226" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F226" s="2">
-        <v>1892200</v>
+        <v>4693090</v>
       </c>
       <c r="G226" s="2">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="H226" s="2">
         <v>0</v>
@@ -7661,25 +7661,25 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>430</v>
+        <v>194</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>431</v>
+        <v>195</v>
       </c>
       <c r="D227" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F227" s="2">
-        <v>2977082</v>
+        <v>1210302</v>
       </c>
       <c r="G227" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="H227" s="2">
         <v>0</v>

--- a/data/course_data.xlsx
+++ b/data/course_data.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DF911E-D6D4-47B0-9A8B-A7BB15E2721D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A685D90-127E-4AEE-97F9-BD8B3A54F20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17190" yWindow="6060" windowWidth="16320" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1471,7 +1484,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}" name="Table1" displayName="Table1" ref="A1:H227" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
   <autoFilter ref="A1:H227" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H227">
-    <sortCondition ref="B1:B227"/>
+    <sortCondition descending="1" ref="G1:G227"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E28ED7F9-92E9-43FB-898A-30B6DDD841D3}" name="DepartmentName" dataDxfId="7"/>
@@ -1811,13 +1824,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>261</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -1826,10 +1839,10 @@
         <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>3979315</v>
+        <v>4693090</v>
       </c>
       <c r="G2" s="2">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -1837,25 +1850,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>373</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>374</v>
+        <v>65</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>1098471</v>
+        <v>1121323</v>
       </c>
       <c r="G3" s="2">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -1863,13 +1876,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>277</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>87</v>
+        <v>278</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1878,36 +1891,36 @@
         <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>1307360</v>
+        <v>1875741</v>
       </c>
       <c r="G4" s="2">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="H4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>323</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2">
-        <v>2719999</v>
+        <v>5320332</v>
       </c>
       <c r="G5" s="2">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -1915,51 +1928,51 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>324</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>323</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>1830239</v>
+        <v>3952988</v>
       </c>
       <c r="G6" s="2">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>385</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>386</v>
+        <v>123</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2">
-        <v>1587825</v>
+        <v>7208507</v>
       </c>
       <c r="G7" s="2">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1967,25 +1980,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>350</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>351</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
-        <v>2832797</v>
+        <v>2117533</v>
       </c>
       <c r="G8" s="2">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1993,25 +2006,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>350</v>
+        <v>265</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>351</v>
+        <v>264</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2">
-        <v>2832797</v>
+        <v>1041914</v>
       </c>
       <c r="G9" s="2">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -2019,25 +2032,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2">
-        <v>3070901</v>
+        <v>4828331</v>
       </c>
       <c r="G10" s="2">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -2045,13 +2058,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>198</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -2060,10 +2073,10 @@
         <v>13</v>
       </c>
       <c r="F11" s="2">
-        <v>1666337</v>
+        <v>2923606</v>
       </c>
       <c r="G11" s="2">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -2071,25 +2084,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>395</v>
+        <v>274</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>396</v>
+        <v>276</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2">
-        <v>4205238</v>
+        <v>1739868</v>
       </c>
       <c r="G12" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -2097,77 +2110,77 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2">
-        <v>1583231</v>
+        <v>1635809</v>
       </c>
       <c r="G13" s="2">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="H13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>204</v>
+        <v>88</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="2">
-        <v>3070901</v>
+        <v>9931948</v>
       </c>
       <c r="G14" s="2">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="H14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>325</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>153</v>
+        <v>327</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="2">
-        <v>2355205</v>
+        <v>5320332</v>
       </c>
       <c r="G15" s="2">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -2175,51 +2188,51 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="D16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2">
-        <v>3074554</v>
+        <v>3143825</v>
       </c>
       <c r="G16" s="2">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="H16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>36</v>
+        <v>314</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>315</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F17" s="2">
-        <v>1463803</v>
+        <v>4721220</v>
       </c>
       <c r="G17" s="2">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -2227,25 +2240,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>99</v>
+        <v>372</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>100</v>
+        <v>371</v>
       </c>
       <c r="D18" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F18" s="2">
-        <v>3979315</v>
+        <v>2554019</v>
       </c>
       <c r="G18" s="2">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
@@ -2253,25 +2266,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="D19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2">
-        <v>3074554</v>
+        <v>1540100</v>
       </c>
       <c r="G19" s="2">
-        <v>5</v>
+        <v>138</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -2279,25 +2292,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="D20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2">
-        <v>4419464</v>
+        <v>4693090</v>
       </c>
       <c r="G20" s="2">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="H20" s="2">
         <v>0</v>
@@ -2305,51 +2318,51 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>412</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>413</v>
+        <v>91</v>
       </c>
       <c r="D21" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F21" s="2">
-        <v>2002083</v>
+        <v>9931948</v>
       </c>
       <c r="G21" s="2">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="H21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>398</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>399</v>
       </c>
       <c r="D22" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="2">
-        <v>2719999</v>
+        <v>2994200</v>
       </c>
       <c r="G22" s="2">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
@@ -2357,25 +2370,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>33</v>
+        <v>421</v>
       </c>
       <c r="D23" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="2">
-        <v>1463503</v>
+        <v>1021641</v>
       </c>
       <c r="G23" s="2">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
@@ -2383,25 +2396,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="D24" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F24" s="2">
-        <v>2002083</v>
+        <v>2148154</v>
       </c>
       <c r="G24" s="2">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
@@ -2409,25 +2422,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>105</v>
+        <v>330</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>106</v>
+        <v>331</v>
       </c>
       <c r="D25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="2">
-        <v>2433502</v>
+        <v>1029126</v>
       </c>
       <c r="G25" s="2">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
@@ -2435,25 +2448,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="D26" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2">
-        <v>2355205</v>
+        <v>5320332</v>
       </c>
       <c r="G26" s="2">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -2461,91 +2474,91 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>90</v>
+        <v>422</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>91</v>
+        <v>423</v>
       </c>
       <c r="D27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F27" s="2">
-        <v>9931948</v>
+        <v>2092090</v>
       </c>
       <c r="G27" s="2">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="D28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F28" s="2">
-        <v>9931948</v>
+        <v>3048102</v>
       </c>
       <c r="G28" s="2">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="H28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="D29" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F29" s="2">
-        <v>3143825</v>
+        <v>3218866</v>
       </c>
       <c r="G29" s="2">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="H29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -2554,10 +2567,10 @@
         <v>10</v>
       </c>
       <c r="F30" s="2">
-        <v>9931948</v>
+        <v>2132049</v>
       </c>
       <c r="G30" s="2">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2568,10 +2581,10 @@
         <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D31" s="2">
         <v>2</v>
@@ -2580,33 +2593,33 @@
         <v>10</v>
       </c>
       <c r="F31" s="2">
-        <v>9931948</v>
+        <v>2238227</v>
       </c>
       <c r="G31" s="2">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="H31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>84</v>
+        <v>232</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="D32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F32" s="2">
-        <v>2238227</v>
+        <v>2977082</v>
       </c>
       <c r="G32" s="2">
         <v>120</v>
@@ -2617,25 +2630,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="D33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F33" s="2">
-        <v>3435711</v>
+        <v>3496303</v>
       </c>
       <c r="G33" s="2">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
@@ -2643,25 +2656,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>115</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>116</v>
+        <v>273</v>
       </c>
       <c r="D34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F34" s="2">
-        <v>2903204</v>
+        <v>2579557</v>
       </c>
       <c r="G34" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
@@ -2672,48 +2685,48 @@
         <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="D35" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F35" s="2">
-        <v>3013005</v>
+        <v>1267061</v>
       </c>
       <c r="G35" s="2">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="H35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D36" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F36" s="2">
-        <v>3013005</v>
+        <v>1307360</v>
       </c>
       <c r="G36" s="2">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -2721,25 +2734,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>209</v>
+        <v>264</v>
       </c>
       <c r="D37" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F37" s="2">
-        <v>2238227</v>
+        <v>1041914</v>
       </c>
       <c r="G37" s="2">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -2747,39 +2760,39 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>362</v>
+        <v>119</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>363</v>
+        <v>120</v>
       </c>
       <c r="D38" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F38" s="2">
-        <v>1267061</v>
+        <v>4270666</v>
       </c>
       <c r="G38" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>11</v>
+        <v>220</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>221</v>
       </c>
       <c r="D39" s="2">
         <v>3</v>
@@ -2788,10 +2801,10 @@
         <v>13</v>
       </c>
       <c r="F39" s="2">
-        <v>2107934</v>
+        <v>3041802</v>
       </c>
       <c r="G39" s="2">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2799,25 +2812,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>216</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>217</v>
+        <v>401</v>
       </c>
       <c r="D40" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F40" s="2">
-        <v>3013005</v>
+        <v>2458943</v>
       </c>
       <c r="G40" s="2">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -2825,28 +2838,28 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>210</v>
+        <v>44</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>211</v>
+        <v>45</v>
       </c>
       <c r="D41" s="2">
         <v>3</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F41" s="2">
-        <v>3143825</v>
+        <v>2669297</v>
       </c>
       <c r="G41" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -2854,10 +2867,10 @@
         <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>228</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>229</v>
+        <v>363</v>
       </c>
       <c r="D42" s="2">
         <v>3</v>
@@ -2866,39 +2879,39 @@
         <v>10</v>
       </c>
       <c r="F42" s="2">
-        <v>1842843</v>
+        <v>1267061</v>
       </c>
       <c r="G42" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="H42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>358</v>
+        <v>274</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>359</v>
+        <v>275</v>
       </c>
       <c r="D43" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F43" s="2">
-        <v>3143825</v>
+        <v>2550816</v>
       </c>
       <c r="G43" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -2906,48 +2919,48 @@
         <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>354</v>
+        <v>115</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>355</v>
+        <v>116</v>
       </c>
       <c r="D44" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F44" s="2">
-        <v>7248701</v>
+        <v>2903204</v>
       </c>
       <c r="G44" s="2">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="H44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D45" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F45" s="2">
-        <v>2903204</v>
+        <v>2576518</v>
       </c>
       <c r="G45" s="2">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2955,25 +2968,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="D46" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" s="2">
-        <v>2903204</v>
+        <v>1235319</v>
       </c>
       <c r="G46" s="2">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -2981,51 +2994,51 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="D47" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F47" s="2">
-        <v>1267061</v>
+        <v>1618088</v>
       </c>
       <c r="G47" s="2">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>318</v>
+        <v>230</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>319</v>
+        <v>231</v>
       </c>
       <c r="D48" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F48" s="2">
-        <v>2238227</v>
+        <v>3952988</v>
       </c>
       <c r="G48" s="2">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -3033,25 +3046,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>214</v>
+        <v>274</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="D49" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F49" s="2">
-        <v>2107934</v>
+        <v>4117613</v>
       </c>
       <c r="G49" s="2">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -3059,25 +3072,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>92</v>
+        <v>312</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>93</v>
+        <v>313</v>
       </c>
       <c r="D50" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F50" s="2">
-        <v>7248701</v>
+        <v>3850625</v>
       </c>
       <c r="G50" s="2">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -3085,25 +3098,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>206</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>207</v>
+        <v>371</v>
       </c>
       <c r="D51" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F51" s="2">
-        <v>2903204</v>
+        <v>1214802</v>
       </c>
       <c r="G51" s="2">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -3111,25 +3124,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>360</v>
+        <v>95</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>361</v>
+        <v>96</v>
       </c>
       <c r="D52" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F52" s="2">
-        <v>3435711</v>
+        <v>1318658</v>
       </c>
       <c r="G52" s="2">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -3137,25 +3150,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>94</v>
+        <v>303</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>93</v>
+        <v>304</v>
       </c>
       <c r="D53" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F53" s="2">
-        <v>4321939</v>
+        <v>2832797</v>
       </c>
       <c r="G53" s="2">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -3163,51 +3176,51 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D54" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F54" s="2">
-        <v>2148154</v>
+        <v>9931948</v>
       </c>
       <c r="G54" s="2">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="H54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>128</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>129</v>
+        <v>394</v>
       </c>
       <c r="D55" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F55" s="2">
-        <v>1112262</v>
+        <v>2571190</v>
       </c>
       <c r="G55" s="2">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -3215,25 +3228,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>328</v>
+        <v>113</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>329</v>
+        <v>114</v>
       </c>
       <c r="D56" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F56" s="2">
-        <v>1112262</v>
+        <v>1618088</v>
       </c>
       <c r="G56" s="2">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -3241,25 +3254,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="D57" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F57" s="2">
-        <v>1932179</v>
+        <v>5320332</v>
       </c>
       <c r="G57" s="2">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -3267,25 +3280,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>356</v>
+        <v>158</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>357</v>
+        <v>159</v>
       </c>
       <c r="D58" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F58" s="2">
-        <v>2923606</v>
+        <v>1385355</v>
       </c>
       <c r="G58" s="2">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -3293,25 +3306,25 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>134</v>
+        <v>397</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>135</v>
+        <v>396</v>
       </c>
       <c r="D59" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F59" s="2">
-        <v>1758752</v>
+        <v>5856415</v>
       </c>
       <c r="G59" s="2">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -3319,103 +3332,103 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>144</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>145</v>
+        <v>390</v>
       </c>
       <c r="D60" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F60" s="2">
-        <v>3261519</v>
+        <v>1047857</v>
       </c>
       <c r="G60" s="2">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="H60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>408</v>
+        <v>210</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>409</v>
+        <v>211</v>
       </c>
       <c r="D61" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F61" s="2">
-        <v>7208507</v>
+        <v>3143825</v>
       </c>
       <c r="G61" s="2">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="H61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>30</v>
+        <v>358</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>31</v>
+        <v>359</v>
       </c>
       <c r="D62" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F62" s="2">
-        <v>2814410</v>
+        <v>3143825</v>
       </c>
       <c r="G62" s="2">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="H62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="D63" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F63" s="2">
-        <v>3041802</v>
+        <v>2137934</v>
       </c>
       <c r="G63" s="2">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="H63" s="2">
         <v>0</v>
@@ -3423,25 +3436,25 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>340</v>
+        <v>200</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>341</v>
+        <v>201</v>
       </c>
       <c r="D64" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F64" s="2">
-        <v>4321939</v>
+        <v>5299061</v>
       </c>
       <c r="G64" s="2">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="H64" s="2">
         <v>0</v>
@@ -3452,10 +3465,10 @@
         <v>21</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="D65" s="2">
         <v>4</v>
@@ -3464,10 +3477,10 @@
         <v>13</v>
       </c>
       <c r="F65" s="2">
-        <v>3213466</v>
+        <v>3369135</v>
       </c>
       <c r="G65" s="2">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
@@ -3478,19 +3491,19 @@
         <v>21</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="D66" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F66" s="2">
-        <v>3369135</v>
+        <v>2148154</v>
       </c>
       <c r="G66" s="2">
         <v>82</v>
@@ -3501,25 +3514,25 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D67" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F67" s="2">
-        <v>3261519</v>
+        <v>5475421</v>
       </c>
       <c r="G67" s="2">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
@@ -3527,25 +3540,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>50</v>
+        <v>297</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>51</v>
+        <v>298</v>
       </c>
       <c r="D68" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F68" s="2">
-        <v>1635809</v>
+        <v>2391172</v>
       </c>
       <c r="G68" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="H68" s="2">
         <v>0</v>
@@ -3553,25 +3566,25 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>261</v>
+        <v>132</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>262</v>
+        <v>133</v>
       </c>
       <c r="D69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F69" s="2">
-        <v>4693090</v>
+        <v>1600939</v>
       </c>
       <c r="G69" s="2">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3579,25 +3592,25 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D70" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F70" s="2">
-        <v>1121323</v>
+        <v>5293627</v>
       </c>
       <c r="G70" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="H70" s="2">
         <v>0</v>
@@ -3608,22 +3621,22 @@
         <v>21</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="D71" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F71" s="2">
-        <v>2148154</v>
+        <v>1029126</v>
       </c>
       <c r="G71" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
@@ -3634,22 +3647,22 @@
         <v>21</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="D72" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F72" s="2">
-        <v>2923606</v>
+        <v>3218866</v>
       </c>
       <c r="G72" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -3657,13 +3670,13 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>130</v>
+        <v>307</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>131</v>
+        <v>308</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -3672,36 +3685,36 @@
         <v>10</v>
       </c>
       <c r="F73" s="2">
-        <v>1540100</v>
+        <v>3258742</v>
       </c>
       <c r="G73" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="H73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="D74" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F74" s="2">
-        <v>7208507</v>
+        <v>1842843</v>
       </c>
       <c r="G74" s="2">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="H74" s="2">
         <v>0</v>
@@ -3709,51 +3722,51 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="D75" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F75" s="2">
-        <v>2148154</v>
+        <v>1684669</v>
       </c>
       <c r="G75" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="H75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>78</v>
+        <v>270</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c r="D76" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F76" s="2">
-        <v>3261519</v>
+        <v>1457877</v>
       </c>
       <c r="G76" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H76" s="2">
         <v>0</v>
@@ -3764,22 +3777,22 @@
         <v>21</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>22</v>
+        <v>352</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="D77" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F77" s="2">
-        <v>2117533</v>
+        <v>4721220</v>
       </c>
       <c r="G77" s="2">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3787,25 +3800,25 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>287</v>
+        <v>185</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="D78" s="2">
         <v>3</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F78" s="2">
-        <v>1121323</v>
+        <v>2137934</v>
       </c>
       <c r="G78" s="2">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
@@ -3813,25 +3826,25 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>330</v>
+        <v>391</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>331</v>
+        <v>392</v>
       </c>
       <c r="D79" s="2">
         <v>3</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F79" s="2">
-        <v>1029126</v>
+        <v>1583231</v>
       </c>
       <c r="G79" s="2">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3839,25 +3852,25 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>332</v>
+        <v>377</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="D80" s="2">
         <v>3</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F80" s="2">
-        <v>1029126</v>
+        <v>1198965</v>
       </c>
       <c r="G80" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3865,22 +3878,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>352</v>
+        <v>251</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>353</v>
+        <v>252</v>
       </c>
       <c r="D81" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F81" s="2">
-        <v>4721220</v>
+        <v>3074554</v>
       </c>
       <c r="G81" s="2">
         <v>73</v>
@@ -3891,25 +3904,25 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="D82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="2">
-        <v>3218866</v>
+        <v>2061533</v>
       </c>
       <c r="G82" s="2">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
@@ -3917,22 +3930,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D83" s="2">
         <v>3</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F83" s="2">
-        <v>1540100</v>
+        <v>3013005</v>
       </c>
       <c r="G83" s="2">
         <v>70</v>
@@ -3946,22 +3959,22 @@
         <v>21</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="D84" s="2">
         <v>3</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F84" s="2">
-        <v>4721220</v>
+        <v>1029126</v>
       </c>
       <c r="G84" s="2">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="H84" s="2">
         <v>0</v>
@@ -3972,10 +3985,10 @@
         <v>21</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="D85" s="2">
         <v>3</v>
@@ -3984,10 +3997,10 @@
         <v>13</v>
       </c>
       <c r="F85" s="2">
-        <v>1029126</v>
+        <v>1540100</v>
       </c>
       <c r="G85" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H85" s="2">
         <v>0</v>
@@ -3995,25 +4008,25 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D86" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F86" s="2">
-        <v>3218866</v>
+        <v>1457877</v>
       </c>
       <c r="G86" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
@@ -4021,25 +4034,25 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>42</v>
+        <v>181</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>43</v>
+        <v>182</v>
       </c>
       <c r="D87" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F87" s="2">
-        <v>3218866</v>
+        <v>1767743</v>
       </c>
       <c r="G87" s="2">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
@@ -4047,25 +4060,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>220</v>
+        <v>379</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>221</v>
+        <v>380</v>
       </c>
       <c r="D88" s="2">
         <v>3</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F88" s="2">
-        <v>3041802</v>
+        <v>1561186</v>
       </c>
       <c r="G88" s="2">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="H88" s="2">
         <v>0</v>
@@ -4073,51 +4086,51 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>218</v>
+        <v>56</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="D89" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F89" s="2">
-        <v>3261519</v>
+        <v>2669297</v>
       </c>
       <c r="G89" s="2">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="H89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="D90" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F90" s="2">
-        <v>3496303</v>
+        <v>3261519</v>
       </c>
       <c r="G90" s="2">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
@@ -4125,25 +4138,25 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>322</v>
+        <v>183</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>323</v>
+        <v>184</v>
       </c>
       <c r="D91" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>5320332</v>
+        <v>1740446</v>
       </c>
       <c r="G91" s="2">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -4151,25 +4164,25 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>323</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>5320332</v>
+        <v>3435711</v>
       </c>
       <c r="G92" s="2">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
@@ -4177,25 +4190,25 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>325</v>
+        <v>70</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>326</v>
+        <v>71</v>
       </c>
       <c r="D93" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F93" s="2">
-        <v>5320332</v>
+        <v>4392170</v>
       </c>
       <c r="G93" s="2">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
@@ -4206,22 +4219,22 @@
         <v>21</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>325</v>
+        <v>134</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>327</v>
+        <v>135</v>
       </c>
       <c r="D94" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F94" s="2">
-        <v>5320332</v>
+        <v>1758752</v>
       </c>
       <c r="G94" s="2">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
@@ -4232,22 +4245,22 @@
         <v>19</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>312</v>
+        <v>173</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>313</v>
+        <v>174</v>
       </c>
       <c r="D95" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F95" s="2">
-        <v>3850625</v>
+        <v>1740446</v>
       </c>
       <c r="G95" s="2">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4255,51 +4268,51 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="D96" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F96" s="2">
-        <v>1047857</v>
+        <v>7208507</v>
       </c>
       <c r="G96" s="2">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="H96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>62</v>
+        <v>356</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>63</v>
+        <v>357</v>
       </c>
       <c r="D97" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F97" s="2">
-        <v>1457877</v>
+        <v>2923606</v>
       </c>
       <c r="G97" s="2">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H97" s="2">
         <v>0</v>
@@ -4310,22 +4323,22 @@
         <v>19</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>179</v>
+        <v>338</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>180</v>
+        <v>339</v>
       </c>
       <c r="D98" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F98" s="2">
-        <v>5475421</v>
+        <v>1086552</v>
       </c>
       <c r="G98" s="2">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="H98" s="2">
         <v>0</v>
@@ -4336,22 +4349,22 @@
         <v>19</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>342</v>
+        <v>187</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>343</v>
+        <v>188</v>
       </c>
       <c r="D99" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F99" s="2">
-        <v>2137934</v>
+        <v>1494406</v>
       </c>
       <c r="G99" s="2">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="H99" s="2">
         <v>0</v>
@@ -4359,25 +4372,25 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>188</v>
+        <v>129</v>
       </c>
       <c r="D100" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F100" s="2">
-        <v>1494406</v>
+        <v>1112262</v>
       </c>
       <c r="G100" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H100" s="2">
         <v>0</v>
@@ -4385,25 +4398,25 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>397</v>
+        <v>328</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>396</v>
+        <v>329</v>
       </c>
       <c r="D101" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F101" s="2">
-        <v>5856415</v>
+        <v>1112262</v>
       </c>
       <c r="G101" s="2">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
@@ -4414,22 +4427,22 @@
         <v>19</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>16</v>
+        <v>252</v>
       </c>
       <c r="D102" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F102" s="2">
-        <v>2061533</v>
+        <v>2571190</v>
       </c>
       <c r="G102" s="2">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H102" s="2">
         <v>0</v>
@@ -4437,25 +4450,25 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>70</v>
+        <v>430</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>71</v>
+        <v>431</v>
       </c>
       <c r="D103" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F103" s="2">
-        <v>4392170</v>
+        <v>2977082</v>
       </c>
       <c r="G103" s="2">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="H103" s="2">
         <v>0</v>
@@ -4463,25 +4476,25 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>183</v>
+        <v>336</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>184</v>
+        <v>337</v>
       </c>
       <c r="D104" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F104" s="2">
-        <v>1740446</v>
+        <v>2903204</v>
       </c>
       <c r="G104" s="2">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H104" s="2">
         <v>0</v>
@@ -4489,25 +4502,25 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D105" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F105" s="2">
-        <v>1767743</v>
+        <v>2903204</v>
       </c>
       <c r="G105" s="2">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="H105" s="2">
         <v>0</v>
@@ -4515,25 +4528,25 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>234</v>
+        <v>340</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>235</v>
+        <v>341</v>
       </c>
       <c r="D106" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F106" s="2">
-        <v>3258742</v>
+        <v>4321939</v>
       </c>
       <c r="G106" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H106" s="2">
         <v>0</v>
@@ -4541,25 +4554,25 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>406</v>
+        <v>236</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>407</v>
+        <v>237</v>
       </c>
       <c r="D107" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F107" s="2">
-        <v>5930518</v>
+        <v>6933704</v>
       </c>
       <c r="G107" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="H107" s="2">
         <v>0</v>
@@ -4567,39 +4580,39 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D108" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F108" s="2">
-        <v>2571190</v>
+        <v>1267061</v>
       </c>
       <c r="G108" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H108" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="D109" s="2">
         <v>4</v>
@@ -4608,10 +4621,10 @@
         <v>13</v>
       </c>
       <c r="F109" s="2">
-        <v>2311022</v>
+        <v>3261519</v>
       </c>
       <c r="G109" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H109" s="2">
         <v>0</v>
@@ -4622,22 +4635,22 @@
         <v>19</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>185</v>
+        <v>234</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="D110" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F110" s="2">
-        <v>2137934</v>
+        <v>3258742</v>
       </c>
       <c r="G110" s="2">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
@@ -4645,25 +4658,25 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>393</v>
+        <v>124</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>394</v>
+        <v>125</v>
       </c>
       <c r="D111" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F111" s="2">
-        <v>2571190</v>
+        <v>2148154</v>
       </c>
       <c r="G111" s="2">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
@@ -4671,13 +4684,13 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>381</v>
+        <v>287</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>382</v>
+        <v>288</v>
       </c>
       <c r="D112" s="2">
         <v>3</v>
@@ -4686,10 +4699,10 @@
         <v>13</v>
       </c>
       <c r="F112" s="2">
-        <v>5475421</v>
+        <v>1121323</v>
       </c>
       <c r="G112" s="2">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
@@ -4700,22 +4713,22 @@
         <v>19</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>154</v>
+        <v>249</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>155</v>
+        <v>250</v>
       </c>
       <c r="D113" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F113" s="2">
-        <v>1767743</v>
+        <v>2571190</v>
       </c>
       <c r="G113" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H113" s="2">
         <v>0</v>
@@ -4723,39 +4736,39 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>414</v>
+        <v>354</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D114" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F114" s="2">
-        <v>5856415</v>
+        <v>7248701</v>
       </c>
       <c r="G114" s="2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>316</v>
+        <v>42</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>317</v>
+        <v>43</v>
       </c>
       <c r="D115" s="2">
         <v>3</v>
@@ -4764,10 +4777,10 @@
         <v>13</v>
       </c>
       <c r="F115" s="2">
-        <v>1093367</v>
+        <v>3218866</v>
       </c>
       <c r="G115" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H115" s="2">
         <v>0</v>
@@ -4778,22 +4791,22 @@
         <v>19</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>76</v>
+        <v>364</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="D116" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F116" s="2">
-        <v>5715408</v>
+        <v>2757489</v>
       </c>
       <c r="G116" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H116" s="2">
         <v>0</v>
@@ -4801,13 +4814,13 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="D117" s="2">
         <v>4</v>
@@ -4816,10 +4829,10 @@
         <v>13</v>
       </c>
       <c r="F117" s="2">
-        <v>1086552</v>
+        <v>3435711</v>
       </c>
       <c r="G117" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H117" s="2">
         <v>0</v>
@@ -4830,22 +4843,22 @@
         <v>19</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>121</v>
+        <v>320</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>120</v>
+        <v>321</v>
       </c>
       <c r="D118" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F118" s="2">
-        <v>5293627</v>
+        <v>1086552</v>
       </c>
       <c r="G118" s="2">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="H118" s="2">
         <v>0</v>
@@ -4856,10 +4869,10 @@
         <v>19</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="D119" s="2">
         <v>4</v>
@@ -4868,10 +4881,10 @@
         <v>13</v>
       </c>
       <c r="F119" s="2">
-        <v>1093367</v>
+        <v>1090407</v>
       </c>
       <c r="G119" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
@@ -4882,22 +4895,22 @@
         <v>19</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="D120" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F120" s="2">
-        <v>1086552</v>
+        <v>1093367</v>
       </c>
       <c r="G120" s="2">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H120" s="2">
         <v>0</v>
@@ -4908,22 +4921,22 @@
         <v>19</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D121" s="2">
         <v>4</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F121" s="2">
-        <v>1740446</v>
+        <v>1093367</v>
       </c>
       <c r="G121" s="2">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="H121" s="2">
         <v>0</v>
@@ -4934,10 +4947,10 @@
         <v>19</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>364</v>
+        <v>175</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>365</v>
+        <v>176</v>
       </c>
       <c r="D122" s="2">
         <v>4</v>
@@ -4946,10 +4959,10 @@
         <v>13</v>
       </c>
       <c r="F122" s="2">
-        <v>2757489</v>
+        <v>2311022</v>
       </c>
       <c r="G122" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H122" s="2">
         <v>0</v>
@@ -4960,22 +4973,22 @@
         <v>19</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="D123" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F123" s="2">
-        <v>1086552</v>
+        <v>5715408</v>
       </c>
       <c r="G123" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H123" s="2">
         <v>0</v>
@@ -4986,22 +4999,22 @@
         <v>19</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>295</v>
+        <v>154</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>296</v>
+        <v>155</v>
       </c>
       <c r="D124" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F124" s="2">
-        <v>2311022</v>
+        <v>1767743</v>
       </c>
       <c r="G124" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H124" s="2">
         <v>0</v>
@@ -5035,13 +5048,13 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="D126" s="2">
         <v>4</v>
@@ -5050,10 +5063,10 @@
         <v>13</v>
       </c>
       <c r="F126" s="2">
-        <v>1090407</v>
+        <v>3258742</v>
       </c>
       <c r="G126" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H126" s="2">
         <v>0</v>
@@ -5061,25 +5074,25 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>370</v>
+        <v>293</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>371</v>
+        <v>294</v>
       </c>
       <c r="D127" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F127" s="2">
-        <v>1214802</v>
+        <v>3013005</v>
       </c>
       <c r="G127" s="2">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="H127" s="2">
         <v>0</v>
@@ -5087,51 +5100,51 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>58</v>
+        <v>406</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>59</v>
+        <v>407</v>
       </c>
       <c r="D128" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F128" s="2">
-        <v>1684669</v>
+        <v>5930518</v>
       </c>
       <c r="G128" s="2">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="H128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="D129" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F129" s="2">
-        <v>2977082</v>
+        <v>2107934</v>
       </c>
       <c r="G129" s="2">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="H129" s="2">
         <v>0</v>
@@ -5139,25 +5152,25 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>158</v>
+        <v>334</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>159</v>
+        <v>335</v>
       </c>
       <c r="D130" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F130" s="2">
-        <v>1385355</v>
+        <v>1932179</v>
       </c>
       <c r="G130" s="2">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="H130" s="2">
         <v>0</v>
@@ -5165,25 +5178,25 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>158</v>
+        <v>414</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>159</v>
+        <v>415</v>
       </c>
       <c r="D131" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F131" s="2">
-        <v>1385355</v>
+        <v>5856415</v>
       </c>
       <c r="G131" s="2">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H131" s="2">
         <v>0</v>
@@ -5191,25 +5204,25 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="D132" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F132" s="2">
-        <v>1041914</v>
+        <v>1210302</v>
       </c>
       <c r="G132" s="2">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="H132" s="2">
         <v>0</v>
@@ -5217,25 +5230,25 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>297</v>
+        <v>171</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>298</v>
+        <v>172</v>
       </c>
       <c r="D133" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F133" s="2">
-        <v>2391172</v>
+        <v>1086552</v>
       </c>
       <c r="G133" s="2">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="H133" s="2">
         <v>0</v>
@@ -5243,25 +5256,25 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>420</v>
+        <v>94</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>421</v>
+        <v>93</v>
       </c>
       <c r="D134" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F134" s="2">
-        <v>1021641</v>
+        <v>4321939</v>
       </c>
       <c r="G134" s="2">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="H134" s="2">
         <v>0</v>
@@ -5272,22 +5285,22 @@
         <v>14</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>15</v>
+        <v>410</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>16</v>
+        <v>411</v>
       </c>
       <c r="D135" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F135" s="2">
-        <v>3048102</v>
+        <v>1214802</v>
       </c>
       <c r="G135" s="2">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="H135" s="2">
         <v>0</v>
@@ -5295,25 +5308,25 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>422</v>
+        <v>208</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>423</v>
+        <v>209</v>
       </c>
       <c r="D136" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F136" s="2">
-        <v>2092090</v>
+        <v>2238227</v>
       </c>
       <c r="G136" s="2">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="H136" s="2">
         <v>0</v>
@@ -5321,25 +5334,25 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>400</v>
+        <v>295</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>401</v>
+        <v>296</v>
       </c>
       <c r="D137" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F137" s="2">
-        <v>2458943</v>
+        <v>2311022</v>
       </c>
       <c r="G137" s="2">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="H137" s="2">
         <v>0</v>
@@ -5350,48 +5363,48 @@
         <v>14</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>308</v>
+        <v>367</v>
       </c>
       <c r="D138" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F138" s="2">
-        <v>3258742</v>
+        <v>2092090</v>
       </c>
       <c r="G138" s="2">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="H138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>119</v>
+        <v>285</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>120</v>
+        <v>286</v>
       </c>
       <c r="D139" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F139" s="2">
-        <v>4270666</v>
+        <v>3041802</v>
       </c>
       <c r="G139" s="2">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="H139" s="2">
         <v>0</v>
@@ -5399,25 +5412,25 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>44</v>
+        <v>222</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>45</v>
+        <v>223</v>
       </c>
       <c r="D140" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F140" s="2">
-        <v>2669297</v>
+        <v>3213466</v>
       </c>
       <c r="G140" s="2">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="H140" s="2">
         <v>0</v>
@@ -5425,25 +5438,25 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>95</v>
+        <v>381</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="D141" s="2">
         <v>3</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F141" s="2">
-        <v>1318658</v>
+        <v>5475421</v>
       </c>
       <c r="G141" s="2">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="H141" s="2">
         <v>0</v>
@@ -5454,22 +5467,22 @@
         <v>14</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="D142" s="2">
         <v>3</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F142" s="2">
-        <v>1583231</v>
+        <v>5213213</v>
       </c>
       <c r="G142" s="2">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="H142" s="2">
         <v>0</v>
@@ -5480,22 +5493,22 @@
         <v>14</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>377</v>
+        <v>289</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>378</v>
+        <v>290</v>
       </c>
       <c r="D143" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F143" s="2">
-        <v>1198965</v>
+        <v>2028216</v>
       </c>
       <c r="G143" s="2">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="H143" s="2">
         <v>0</v>
@@ -5503,74 +5516,74 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>379</v>
+        <v>54</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>380</v>
+        <v>55</v>
       </c>
       <c r="D144" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F144" s="2">
-        <v>1561186</v>
+        <v>6112322</v>
       </c>
       <c r="G144" s="2">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="H144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>56</v>
+        <v>318</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>57</v>
+        <v>319</v>
       </c>
       <c r="D145" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F145" s="2">
-        <v>2669297</v>
+        <v>2238227</v>
       </c>
       <c r="G145" s="2">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="H145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="D146" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F146" s="2">
-        <v>3048102</v>
+        <v>3261519</v>
       </c>
       <c r="G146" s="2">
         <v>23</v>
@@ -5584,10 +5597,10 @@
         <v>14</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>430</v>
+        <v>202</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>431</v>
+        <v>203</v>
       </c>
       <c r="D147" s="2">
         <v>3</v>
@@ -5596,10 +5609,10 @@
         <v>13</v>
       </c>
       <c r="F147" s="2">
-        <v>2977082</v>
+        <v>3048102</v>
       </c>
       <c r="G147" s="2">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="H147" s="2">
         <v>0</v>
@@ -5607,25 +5620,25 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>418</v>
+        <v>28</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>419</v>
+        <v>29</v>
       </c>
       <c r="D148" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F148" s="2">
-        <v>5213213</v>
+        <v>2719999</v>
       </c>
       <c r="G148" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H148" s="2">
         <v>0</v>
@@ -5636,22 +5649,22 @@
         <v>14</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>236</v>
+        <v>402</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>237</v>
+        <v>403</v>
       </c>
       <c r="D149" s="2">
         <v>4</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F149" s="2">
-        <v>6933704</v>
+        <v>2234229</v>
       </c>
       <c r="G149" s="2">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="H149" s="2">
         <v>0</v>
@@ -5659,25 +5672,25 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>138</v>
+        <v>387</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>139</v>
+        <v>388</v>
       </c>
       <c r="D150" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F150" s="2">
-        <v>3524624</v>
+        <v>1235319</v>
       </c>
       <c r="G150" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H150" s="2">
         <v>0</v>
@@ -5714,10 +5727,10 @@
         <v>14</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>366</v>
+        <v>305</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>367</v>
+        <v>306</v>
       </c>
       <c r="D152" s="2">
         <v>4</v>
@@ -5726,10 +5739,10 @@
         <v>13</v>
       </c>
       <c r="F152" s="2">
-        <v>2092090</v>
+        <v>3979315</v>
       </c>
       <c r="G152" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H152" s="2">
         <v>0</v>
@@ -5737,25 +5750,25 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>402</v>
+        <v>241</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>403</v>
+        <v>242</v>
       </c>
       <c r="D153" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F153" s="2">
-        <v>2234229</v>
+        <v>4576344</v>
       </c>
       <c r="G153" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
@@ -5763,13 +5776,13 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>410</v>
+        <v>240</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>411</v>
+        <v>239</v>
       </c>
       <c r="D154" s="2">
         <v>4</v>
@@ -5778,10 +5791,10 @@
         <v>13</v>
       </c>
       <c r="F154" s="2">
-        <v>1214802</v>
+        <v>5318224</v>
       </c>
       <c r="G154" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H154" s="2">
         <v>0</v>
@@ -5789,13 +5802,13 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>426</v>
+        <v>348</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>427</v>
+        <v>349</v>
       </c>
       <c r="D155" s="2">
         <v>4</v>
@@ -5804,24 +5817,24 @@
         <v>13</v>
       </c>
       <c r="F155" s="2">
-        <v>3524624</v>
+        <v>2832797</v>
       </c>
       <c r="G155" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>289</v>
+        <v>344</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="D156" s="2">
         <v>4</v>
@@ -5830,10 +5843,10 @@
         <v>13</v>
       </c>
       <c r="F156" s="2">
-        <v>2028216</v>
+        <v>3371830</v>
       </c>
       <c r="G156" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H156" s="2">
         <v>0</v>
@@ -5841,25 +5854,25 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>306</v>
+        <v>98</v>
       </c>
       <c r="D157" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F157" s="2">
         <v>3979315</v>
       </c>
       <c r="G157" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
@@ -5867,25 +5880,25 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>190</v>
+        <v>374</v>
       </c>
       <c r="D158" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F158" s="2">
-        <v>3258742</v>
+        <v>1098471</v>
       </c>
       <c r="G158" s="2">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H158" s="2">
         <v>0</v>
@@ -5893,25 +5906,25 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>168</v>
+        <v>93</v>
       </c>
       <c r="D159" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F159" s="2">
-        <v>1098471</v>
+        <v>7248701</v>
       </c>
       <c r="G159" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H159" s="2">
         <v>0</v>
@@ -5922,10 +5935,10 @@
         <v>17</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="D160" s="2">
         <v>1</v>
@@ -5934,10 +5947,10 @@
         <v>10</v>
       </c>
       <c r="F160" s="2">
-        <v>1498302</v>
+        <v>1385355</v>
       </c>
       <c r="G160" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H160" s="2">
         <v>0</v>
@@ -5945,51 +5958,51 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>67</v>
+        <v>280</v>
       </c>
       <c r="D161" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F161" s="2">
-        <v>1410757</v>
+        <v>1457877</v>
       </c>
       <c r="G161" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="D162" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F162" s="2">
-        <v>1098471</v>
+        <v>5018255</v>
       </c>
       <c r="G162" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H162" s="2">
         <v>0</v>
@@ -5997,25 +6010,25 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="D163" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F163" s="2">
-        <v>1410757</v>
+        <v>5299061</v>
       </c>
       <c r="G163" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H163" s="2">
         <v>0</v>
@@ -6023,25 +6036,25 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D164" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F164" s="2">
-        <v>3633158</v>
+        <v>1875741</v>
       </c>
       <c r="G164" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H164" s="2">
         <v>0</v>
@@ -6049,51 +6062,51 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>291</v>
+        <v>86</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>292</v>
+        <v>87</v>
       </c>
       <c r="D165" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F165" s="2">
-        <v>1009202</v>
+        <v>1307360</v>
       </c>
       <c r="G165" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H165" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>376</v>
+        <v>323</v>
       </c>
       <c r="D166" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F166" s="2">
-        <v>1410757</v>
+        <v>1830239</v>
       </c>
       <c r="G166" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H166" s="2">
         <v>0</v>
@@ -6101,25 +6114,25 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>196</v>
+        <v>385</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>197</v>
+        <v>386</v>
       </c>
       <c r="D167" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F167" s="2">
-        <v>2190106</v>
+        <v>1587825</v>
       </c>
       <c r="G167" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H167" s="2">
         <v>0</v>
@@ -6127,25 +6140,25 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>281</v>
+        <v>395</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>282</v>
+        <v>396</v>
       </c>
       <c r="D168" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F168" s="2">
-        <v>1009202</v>
+        <v>4205238</v>
       </c>
       <c r="G168" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -6153,25 +6166,25 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>346</v>
+        <v>251</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>347</v>
+        <v>252</v>
       </c>
       <c r="D169" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F169" s="2">
-        <v>2446060</v>
+        <v>3074554</v>
       </c>
       <c r="G169" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H169" s="2">
         <v>0</v>
@@ -6179,25 +6192,25 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="D170" s="2">
         <v>3</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F170" s="2">
-        <v>1892200</v>
+        <v>1707115</v>
       </c>
       <c r="G170" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H170" s="2">
         <v>0</v>
@@ -6205,25 +6218,25 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>245</v>
+        <v>103</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="D171" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F171" s="2">
-        <v>2446060</v>
+        <v>1494406</v>
       </c>
       <c r="G171" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H171" s="2">
         <v>0</v>
@@ -6231,25 +6244,25 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>248</v>
+        <v>118</v>
       </c>
       <c r="D172" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F172" s="2">
-        <v>1608770</v>
+        <v>2994200</v>
       </c>
       <c r="G172" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -6257,25 +6270,25 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>310</v>
+        <v>416</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>311</v>
+        <v>417</v>
       </c>
       <c r="D173" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F173" s="2">
-        <v>3633158</v>
+        <v>3334973</v>
       </c>
       <c r="G173" s="2">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H173" s="2">
         <v>0</v>
@@ -6283,25 +6296,25 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>255</v>
+        <v>25</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="D174" s="2">
         <v>4</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F174" s="2">
-        <v>1608770</v>
+        <v>1502554</v>
       </c>
       <c r="G174" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H174" s="2">
         <v>0</v>
@@ -6309,25 +6322,25 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="D175" s="2">
         <v>4</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F175" s="2">
-        <v>3258742</v>
+        <v>1618088</v>
       </c>
       <c r="G175" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H175" s="2">
         <v>0</v>
@@ -6335,25 +6348,25 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>424</v>
+        <v>150</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>425</v>
+        <v>151</v>
       </c>
       <c r="D176" s="2">
         <v>4</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F176" s="2">
-        <v>5997408</v>
+        <v>5018255</v>
       </c>
       <c r="G176" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H176" s="2">
         <v>0</v>
@@ -6361,25 +6374,25 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="D177" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F177" s="2">
-        <v>1498302</v>
+        <v>3070901</v>
       </c>
       <c r="G177" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H177" s="2">
         <v>0</v>
@@ -6390,22 +6403,22 @@
         <v>17</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>404</v>
+        <v>167</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>405</v>
+        <v>168</v>
       </c>
       <c r="D178" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F178" s="2">
-        <v>1410757</v>
+        <v>1098471</v>
       </c>
       <c r="G178" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H178" s="2">
         <v>0</v>
@@ -6413,25 +6426,25 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>251</v>
+        <v>48</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="D179" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F179" s="2">
-        <v>1267061</v>
+        <v>2579557</v>
       </c>
       <c r="G179" s="2">
-        <v>115</v>
+        <v>16</v>
       </c>
       <c r="H179" s="2">
         <v>1</v>
@@ -6439,25 +6452,25 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>251</v>
+        <v>142</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>252</v>
+        <v>143</v>
       </c>
       <c r="D180" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F180" s="2">
-        <v>3074554</v>
+        <v>1502554</v>
       </c>
       <c r="G180" s="2">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H180" s="2">
         <v>0</v>
@@ -6468,22 +6481,22 @@
         <v>27</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>252</v>
+        <v>308</v>
       </c>
       <c r="D181" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F181" s="2">
-        <v>3074554</v>
+        <v>3070901</v>
       </c>
       <c r="G181" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H181" s="2">
         <v>0</v>
@@ -6491,25 +6504,25 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>251</v>
+        <v>36</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>252</v>
+        <v>37</v>
       </c>
       <c r="D182" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F182" s="2">
-        <v>2571190</v>
+        <v>1463803</v>
       </c>
       <c r="G182" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
@@ -6517,51 +6530,51 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D183" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F183" s="2">
-        <v>3952988</v>
+        <v>2719999</v>
       </c>
       <c r="G183" s="2">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="H183" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>372</v>
+        <v>138</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>371</v>
+        <v>139</v>
       </c>
       <c r="D184" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F184" s="2">
-        <v>2554019</v>
+        <v>3524624</v>
       </c>
       <c r="G184" s="2">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="H184" s="2">
         <v>0</v>
@@ -6569,25 +6582,25 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>60</v>
+        <v>426</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>59</v>
+        <v>427</v>
       </c>
       <c r="D185" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F185" s="2">
-        <v>1307360</v>
+        <v>3524624</v>
       </c>
       <c r="G185" s="2">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="H185" s="2">
         <v>0</v>
@@ -6598,22 +6611,22 @@
         <v>24</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="D186" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F186" s="2">
-        <v>2132049</v>
+        <v>2576518</v>
       </c>
       <c r="G186" s="2">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
@@ -6621,13 +6634,13 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="D187" s="2">
         <v>1</v>
@@ -6636,10 +6649,10 @@
         <v>10</v>
       </c>
       <c r="F187" s="2">
-        <v>1041914</v>
+        <v>2550816</v>
       </c>
       <c r="G187" s="2">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="H187" s="2">
         <v>0</v>
@@ -6647,25 +6660,25 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>302</v>
+        <v>351</v>
       </c>
       <c r="D188" s="2">
         <v>2</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F188" s="2">
-        <v>1235319</v>
+        <v>2832797</v>
       </c>
       <c r="G188" s="2">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="H188" s="2">
         <v>0</v>
@@ -6673,25 +6686,25 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>299</v>
+        <v>72</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>300</v>
+        <v>73</v>
       </c>
       <c r="D189" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F189" s="2">
-        <v>1618088</v>
+        <v>3074554</v>
       </c>
       <c r="G189" s="2">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="H189" s="2">
         <v>0</v>
@@ -6699,25 +6712,25 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>398</v>
+        <v>32</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>399</v>
+        <v>33</v>
       </c>
       <c r="D190" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F190" s="2">
-        <v>2994200</v>
+        <v>1463503</v>
       </c>
       <c r="G190" s="2">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -6725,25 +6738,25 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="D191" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F191" s="2">
-        <v>1618088</v>
+        <v>2814410</v>
       </c>
       <c r="G191" s="2">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
@@ -6751,25 +6764,25 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>303</v>
+        <v>218</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>304</v>
+        <v>219</v>
       </c>
       <c r="D192" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F192" s="2">
-        <v>2832797</v>
+        <v>3261519</v>
       </c>
       <c r="G192" s="2">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="H192" s="2">
         <v>0</v>
@@ -6780,22 +6793,22 @@
         <v>24</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>132</v>
+        <v>383</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>133</v>
+        <v>384</v>
       </c>
       <c r="D193" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F193" s="2">
-        <v>1600939</v>
+        <v>1235319</v>
       </c>
       <c r="G193" s="2">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -6803,25 +6816,25 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="D194" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F194" s="2">
-        <v>2579557</v>
+        <v>1666337</v>
       </c>
       <c r="G194" s="2">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
@@ -6829,25 +6842,25 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>230</v>
+        <v>148</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>231</v>
+        <v>149</v>
       </c>
       <c r="D195" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F195" s="2">
-        <v>3952988</v>
+        <v>9931948</v>
       </c>
       <c r="G195" s="2">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="H195" s="2">
         <v>0</v>
@@ -6855,25 +6868,25 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>270</v>
+        <v>61</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>271</v>
+        <v>59</v>
       </c>
       <c r="D196" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F196" s="2">
-        <v>1457877</v>
+        <v>1498302</v>
       </c>
       <c r="G196" s="2">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="H196" s="2">
         <v>0</v>
@@ -6881,25 +6894,25 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>201</v>
+        <v>12</v>
       </c>
       <c r="D197" s="2">
         <v>3</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F197" s="2">
-        <v>5299061</v>
+        <v>2107934</v>
       </c>
       <c r="G197" s="2">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="H197" s="2">
         <v>0</v>
@@ -6907,51 +6920,51 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>226</v>
+        <v>66</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="D198" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F198" s="2">
-        <v>2576518</v>
+        <v>1410757</v>
       </c>
       <c r="G198" s="2">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="H198" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>368</v>
+        <v>152</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>369</v>
+        <v>153</v>
       </c>
       <c r="D199" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F199" s="2">
-        <v>1707115</v>
+        <v>2355205</v>
       </c>
       <c r="G199" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H199" s="2">
         <v>0</v>
@@ -6959,13 +6972,13 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="D200" s="2">
         <v>3</v>
@@ -6974,10 +6987,10 @@
         <v>13</v>
       </c>
       <c r="F200" s="2">
-        <v>1235319</v>
+        <v>2002083</v>
       </c>
       <c r="G200" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H200" s="2">
         <v>0</v>
@@ -6985,25 +6998,25 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>242</v>
+        <v>106</v>
       </c>
       <c r="D201" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F201" s="2">
-        <v>4576344</v>
+        <v>2433502</v>
       </c>
       <c r="G201" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H201" s="2">
         <v>0</v>
@@ -7011,25 +7024,25 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="D202" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F202" s="2">
-        <v>5318224</v>
+        <v>3013005</v>
       </c>
       <c r="G202" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
@@ -7037,39 +7050,39 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="D203" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F203" s="2">
-        <v>1494406</v>
+        <v>1583231</v>
       </c>
       <c r="G203" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H203" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="D204" s="2">
         <v>4</v>
@@ -7078,62 +7091,62 @@
         <v>13</v>
       </c>
       <c r="F204" s="2">
-        <v>2579557</v>
+        <v>2002083</v>
       </c>
       <c r="G204" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H204" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>54</v>
+        <v>255</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>55</v>
+        <v>256</v>
       </c>
       <c r="D205" s="2">
         <v>4</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F205" s="2">
-        <v>6112322</v>
+        <v>1608770</v>
       </c>
       <c r="G205" s="2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H205" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D206" s="2">
         <v>4</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F206" s="2">
-        <v>1618088</v>
+        <v>3258742</v>
       </c>
       <c r="G206" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H206" s="2">
         <v>0</v>
@@ -7141,25 +7154,25 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="D207" s="2">
         <v>4</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F207" s="2">
-        <v>1235319</v>
+        <v>5997408</v>
       </c>
       <c r="G207" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H207" s="2">
         <v>0</v>
@@ -7167,13 +7180,13 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>279</v>
+        <v>238</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="D208" s="2">
         <v>4</v>
@@ -7182,10 +7195,10 @@
         <v>13</v>
       </c>
       <c r="F208" s="2">
-        <v>1457877</v>
+        <v>2355205</v>
       </c>
       <c r="G208" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H208" s="2">
         <v>0</v>
@@ -7193,25 +7206,25 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>151</v>
+        <v>269</v>
       </c>
       <c r="D209" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F209" s="2">
-        <v>5018255</v>
+        <v>3633158</v>
       </c>
       <c r="G209" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H209" s="2">
         <v>0</v>
@@ -7219,25 +7232,25 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>156</v>
+        <v>291</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>157</v>
+        <v>292</v>
       </c>
       <c r="D210" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F210" s="2">
-        <v>5018255</v>
+        <v>1009202</v>
       </c>
       <c r="G210" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
@@ -7245,25 +7258,25 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>117</v>
+        <v>375</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>118</v>
+        <v>376</v>
       </c>
       <c r="D211" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F211" s="2">
-        <v>2994200</v>
+        <v>1410757</v>
       </c>
       <c r="G211" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H211" s="2">
         <v>0</v>
@@ -7271,13 +7284,13 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="D212" s="2">
         <v>4</v>
@@ -7286,10 +7299,10 @@
         <v>13</v>
       </c>
       <c r="F212" s="2">
-        <v>2576518</v>
+        <v>1498302</v>
       </c>
       <c r="G212" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H212" s="2">
         <v>0</v>
@@ -7297,13 +7310,13 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>224</v>
+        <v>404</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>225</v>
+        <v>405</v>
       </c>
       <c r="D213" s="2">
         <v>4</v>
@@ -7312,10 +7325,10 @@
         <v>13</v>
       </c>
       <c r="F213" s="2">
-        <v>5299061</v>
+        <v>1410757</v>
       </c>
       <c r="G213" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H213" s="2">
         <v>0</v>
@@ -7323,51 +7336,51 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>348</v>
+        <v>99</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>349</v>
+        <v>100</v>
       </c>
       <c r="D214" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F214" s="2">
-        <v>2832797</v>
+        <v>3979315</v>
       </c>
       <c r="G214" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H214" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D215" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F215" s="2">
-        <v>1502554</v>
+        <v>4419464</v>
       </c>
       <c r="G215" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H215" s="2">
         <v>0</v>
@@ -7375,25 +7388,25 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>416</v>
+        <v>18</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>417</v>
+        <v>16</v>
       </c>
       <c r="D216" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F216" s="2">
-        <v>3334973</v>
+        <v>1098471</v>
       </c>
       <c r="G216" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H216" s="2">
         <v>0</v>
@@ -7401,25 +7414,25 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>344</v>
+        <v>196</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>345</v>
+        <v>197</v>
       </c>
       <c r="D217" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F217" s="2">
-        <v>3371830</v>
+        <v>2190106</v>
       </c>
       <c r="G217" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H217" s="2">
         <v>0</v>
@@ -7427,25 +7440,25 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>25</v>
+        <v>350</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
       <c r="D218" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F218" s="2">
-        <v>1502554</v>
+        <v>2832797</v>
       </c>
       <c r="G218" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H218" s="2">
         <v>0</v>
@@ -7453,25 +7466,25 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="D219" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F219" s="2">
-        <v>4828331</v>
+        <v>1410757</v>
       </c>
       <c r="G219" s="2">
-        <v>160</v>
+        <v>6</v>
       </c>
       <c r="H219" s="2">
         <v>0</v>
@@ -7479,25 +7492,25 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D220" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F220" s="2">
-        <v>1875741</v>
+        <v>1009202</v>
       </c>
       <c r="G220" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H220" s="2">
         <v>0</v>
@@ -7505,25 +7518,25 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>277</v>
+        <v>346</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>278</v>
+        <v>347</v>
       </c>
       <c r="D221" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F221" s="2">
-        <v>1875741</v>
+        <v>2446060</v>
       </c>
       <c r="G221" s="2">
-        <v>189</v>
+        <v>6</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
@@ -7531,25 +7544,25 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>274</v>
+        <v>68</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>275</v>
+        <v>69</v>
       </c>
       <c r="D222" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F222" s="2">
-        <v>2550816</v>
+        <v>3074554</v>
       </c>
       <c r="G222" s="2">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="H222" s="2">
         <v>0</v>
@@ -7560,22 +7573,22 @@
         <v>17</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>274</v>
+        <v>428</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>275</v>
+        <v>429</v>
       </c>
       <c r="D223" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F223" s="2">
-        <v>2550816</v>
+        <v>1892200</v>
       </c>
       <c r="G223" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H223" s="2">
         <v>0</v>
@@ -7583,25 +7596,25 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="D224" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F224" s="2">
-        <v>4117613</v>
+        <v>2446060</v>
       </c>
       <c r="G224" s="2">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="H224" s="2">
         <v>0</v>
@@ -7609,25 +7622,25 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="D225" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F225" s="2">
-        <v>1739868</v>
+        <v>1608770</v>
       </c>
       <c r="G225" s="2">
-        <v>159</v>
+        <v>5</v>
       </c>
       <c r="H225" s="2">
         <v>0</v>
@@ -7635,25 +7648,25 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>259</v>
+        <v>310</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="D226" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F226" s="2">
-        <v>4693090</v>
+        <v>3633158</v>
       </c>
       <c r="G226" s="2">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="H226" s="2">
         <v>0</v>
@@ -7661,13 +7674,13 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="D227" s="2">
         <v>4</v>
@@ -7676,10 +7689,10 @@
         <v>13</v>
       </c>
       <c r="F227" s="2">
-        <v>1210302</v>
+        <v>2903204</v>
       </c>
       <c r="G227" s="2">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H227" s="2">
         <v>0</v>

--- a/data/course_data.xlsx
+++ b/data/course_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A685D90-127E-4AEE-97F9-BD8B3A54F20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10656E90-4A94-4C86-86A2-83F8E78E7352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1482,7 +1482,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}" name="Table1" displayName="Table1" ref="A1:H227" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
-  <autoFilter ref="A1:H227" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}"/>
+  <autoFilter ref="A1:H227" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Elektrik-Elektronik Mühendisliği"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="4"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H227">
     <sortCondition descending="1" ref="G1:G227"/>
   </sortState>
@@ -1822,7 +1833,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1848,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -1874,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -1900,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -1926,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1952,7 +1963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -1978,7 +1989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -2004,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -2030,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -2056,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -2082,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -2108,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2134,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -2160,7 +2171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2186,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2212,7 +2223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
@@ -2238,7 +2249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -2264,7 +2275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
@@ -2290,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -2316,7 +2327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -2342,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -2368,7 +2379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
@@ -2394,7 +2405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
@@ -2420,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
@@ -2446,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
@@ -2472,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
@@ -2498,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
@@ -2524,7 +2535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>21</v>
       </c>
@@ -2550,7 +2561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -2576,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
@@ -2602,7 +2613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>14</v>
       </c>
@@ -2628,7 +2639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -2654,7 +2665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
@@ -2680,7 +2691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>7</v>
       </c>
@@ -2706,7 +2717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>24</v>
       </c>
@@ -2732,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
@@ -2758,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
@@ -2784,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>21</v>
       </c>
@@ -2810,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -2836,7 +2847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
@@ -2862,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
@@ -2888,7 +2899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>14</v>
       </c>
@@ -2914,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -2940,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>24</v>
       </c>
@@ -2966,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>24</v>
       </c>
@@ -2992,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
@@ -3018,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>24</v>
       </c>
@@ -3044,7 +3055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>19</v>
       </c>
@@ -3070,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>19</v>
       </c>
@@ -3096,7 +3107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>14</v>
       </c>
@@ -3122,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>14</v>
       </c>
@@ -3148,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>24</v>
       </c>
@@ -3174,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -3200,7 +3211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>19</v>
       </c>
@@ -3226,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>24</v>
       </c>
@@ -3252,7 +3263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>7</v>
       </c>
@@ -3278,7 +3289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>14</v>
       </c>
@@ -3304,7 +3315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>19</v>
       </c>
@@ -3330,7 +3341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>19</v>
       </c>
@@ -3356,7 +3367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>7</v>
       </c>
@@ -3382,7 +3393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>7</v>
       </c>
@@ -3408,7 +3419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>19</v>
       </c>
@@ -3434,7 +3445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>24</v>
       </c>
@@ -3486,7 +3497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>21</v>
       </c>
@@ -3512,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>19</v>
       </c>
@@ -3538,7 +3549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>14</v>
       </c>
@@ -3564,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>24</v>
       </c>
@@ -3590,7 +3601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>19</v>
       </c>
@@ -3616,7 +3627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>21</v>
       </c>
@@ -3642,7 +3653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>21</v>
       </c>
@@ -3668,7 +3679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>14</v>
       </c>
@@ -3694,7 +3705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>7</v>
       </c>
@@ -3720,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>14</v>
       </c>
@@ -3746,7 +3757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>24</v>
       </c>
@@ -3772,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>21</v>
       </c>
@@ -3798,7 +3809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>19</v>
       </c>
@@ -3824,7 +3835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>14</v>
       </c>
@@ -3850,7 +3861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>14</v>
       </c>
@@ -3876,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>14</v>
       </c>
@@ -3902,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>19</v>
       </c>
@@ -3928,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>7</v>
       </c>
@@ -3954,7 +3965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>21</v>
       </c>
@@ -3980,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>21</v>
       </c>
@@ -4006,7 +4017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>19</v>
       </c>
@@ -4032,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>19</v>
       </c>
@@ -4058,7 +4069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>14</v>
       </c>
@@ -4084,7 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>14</v>
       </c>
@@ -4110,7 +4121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>21</v>
       </c>
@@ -4136,7 +4147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>19</v>
       </c>
@@ -4162,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
@@ -4188,7 +4199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>19</v>
       </c>
@@ -4240,7 +4251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>19</v>
       </c>
@@ -4318,7 +4329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>19</v>
       </c>
@@ -4344,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>19</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>19</v>
       </c>
@@ -4448,7 +4459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>14</v>
       </c>
@@ -4474,7 +4485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>7</v>
       </c>
@@ -4500,7 +4511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>7</v>
       </c>
@@ -4552,7 +4563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>14</v>
       </c>
@@ -4578,7 +4589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>7</v>
       </c>
@@ -4630,7 +4641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>19</v>
       </c>
@@ -4682,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>21</v>
       </c>
@@ -4708,7 +4719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>19</v>
       </c>
@@ -4734,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>7</v>
       </c>
@@ -4760,7 +4771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>21</v>
       </c>
@@ -4786,7 +4797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>19</v>
       </c>
@@ -4812,7 +4823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>7</v>
       </c>
@@ -4838,7 +4849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>19</v>
       </c>
@@ -4864,7 +4875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>19</v>
       </c>
@@ -4890,7 +4901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>19</v>
       </c>
@@ -4916,7 +4927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>19</v>
       </c>
@@ -4942,7 +4953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>19</v>
       </c>
@@ -4968,7 +4979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>19</v>
       </c>
@@ -4994,7 +5005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>19</v>
       </c>
@@ -5020,7 +5031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>19</v>
       </c>
@@ -5046,7 +5057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>14</v>
       </c>
@@ -5072,7 +5083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>7</v>
       </c>
@@ -5098,7 +5109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>19</v>
       </c>
@@ -5124,7 +5135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>7</v>
       </c>
@@ -5176,7 +5187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>19</v>
       </c>
@@ -5202,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>24</v>
       </c>
@@ -5228,7 +5239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>19</v>
       </c>
@@ -5280,7 +5291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>14</v>
       </c>
@@ -5306,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>7</v>
       </c>
@@ -5332,7 +5343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>19</v>
       </c>
@@ -5358,7 +5369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>14</v>
       </c>
@@ -5436,7 +5447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>19</v>
       </c>
@@ -5462,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>14</v>
       </c>
@@ -5488,7 +5499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>14</v>
       </c>
@@ -5514,7 +5525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>24</v>
       </c>
@@ -5540,7 +5551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>7</v>
       </c>
@@ -5592,7 +5603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>14</v>
       </c>
@@ -5618,7 +5629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>27</v>
       </c>
@@ -5644,7 +5655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>14</v>
       </c>
@@ -5670,7 +5681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>24</v>
       </c>
@@ -5696,7 +5707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>14</v>
       </c>
@@ -5722,7 +5733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>14</v>
       </c>
@@ -5748,7 +5759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>24</v>
       </c>
@@ -5774,7 +5785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>24</v>
       </c>
@@ -5800,7 +5811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>24</v>
       </c>
@@ -5826,7 +5837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>24</v>
       </c>
@@ -5852,7 +5863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>27</v>
       </c>
@@ -5878,7 +5889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>27</v>
       </c>
@@ -5904,7 +5915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>7</v>
       </c>
@@ -5930,7 +5941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>17</v>
       </c>
@@ -5956,7 +5967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>24</v>
       </c>
@@ -5982,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>24</v>
       </c>
@@ -6008,7 +6019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>24</v>
       </c>
@@ -6034,7 +6045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>27</v>
       </c>
@@ -6060,7 +6071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>27</v>
       </c>
@@ -6086,7 +6097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>27</v>
       </c>
@@ -6112,7 +6123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>27</v>
       </c>
@@ -6138,7 +6149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>27</v>
       </c>
@@ -6164,7 +6175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>27</v>
       </c>
@@ -6190,7 +6201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>24</v>
       </c>
@@ -6216,7 +6227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>24</v>
       </c>
@@ -6242,7 +6253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>24</v>
       </c>
@@ -6268,7 +6279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>24</v>
       </c>
@@ -6294,7 +6305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>24</v>
       </c>
@@ -6320,7 +6331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>24</v>
       </c>
@@ -6346,7 +6357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>24</v>
       </c>
@@ -6372,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>27</v>
       </c>
@@ -6398,7 +6409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>17</v>
       </c>
@@ -6424,7 +6435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>24</v>
       </c>
@@ -6450,7 +6461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>24</v>
       </c>
@@ -6476,7 +6487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>27</v>
       </c>
@@ -6502,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>27</v>
       </c>
@@ -6528,7 +6539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>27</v>
       </c>
@@ -6554,7 +6565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>14</v>
       </c>
@@ -6580,7 +6591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>14</v>
       </c>
@@ -6606,7 +6617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>24</v>
       </c>
@@ -6632,7 +6643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>17</v>
       </c>
@@ -6658,7 +6669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>27</v>
       </c>
@@ -6684,7 +6695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>27</v>
       </c>
@@ -6710,7 +6721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>27</v>
       </c>
@@ -6788,7 +6799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>24</v>
       </c>
@@ -6814,7 +6825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>27</v>
       </c>
@@ -6840,7 +6851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>7</v>
       </c>
@@ -6866,7 +6877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>17</v>
       </c>
@@ -6892,7 +6903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>7</v>
       </c>
@@ -6918,7 +6929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>17</v>
       </c>
@@ -6944,7 +6955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>27</v>
       </c>
@@ -6970,7 +6981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>27</v>
       </c>
@@ -6996,7 +7007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>27</v>
       </c>
@@ -7022,7 +7033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>7</v>
       </c>
@@ -7048,7 +7059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>27</v>
       </c>
@@ -7074,7 +7085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>27</v>
       </c>
@@ -7100,7 +7111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>17</v>
       </c>
@@ -7126,7 +7137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>17</v>
       </c>
@@ -7152,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>17</v>
       </c>
@@ -7178,7 +7189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>27</v>
       </c>
@@ -7204,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>17</v>
       </c>
@@ -7230,7 +7241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>17</v>
       </c>
@@ -7256,7 +7267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>17</v>
       </c>
@@ -7282,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>17</v>
       </c>
@@ -7308,7 +7319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>17</v>
       </c>
@@ -7334,7 +7345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>27</v>
       </c>
@@ -7360,7 +7371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>27</v>
       </c>
@@ -7386,7 +7397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>17</v>
       </c>
@@ -7412,7 +7423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>17</v>
       </c>
@@ -7438,7 +7449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>17</v>
       </c>
@@ -7464,7 +7475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>17</v>
       </c>
@@ -7490,7 +7501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>17</v>
       </c>
@@ -7516,7 +7527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>17</v>
       </c>
@@ -7542,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>27</v>
       </c>
@@ -7568,7 +7579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>17</v>
       </c>
@@ -7594,7 +7605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>17</v>
       </c>
@@ -7620,7 +7631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>17</v>
       </c>
@@ -7646,7 +7657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>17</v>
       </c>
@@ -7672,7 +7683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>7</v>
       </c>
